--- a/AHR 28th/AHR_data 28th dashboard.xlsx
+++ b/AHR 28th/AHR_data 28th dashboard.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Individual Scores &amp; Rankings" sheetId="1" r:id="rId1"/>
     <sheet name="State Mileage" sheetId="2" r:id="rId2"/>
     <sheet name="All Rankings" sheetId="3" r:id="rId3"/>
+    <sheet name="AHR Data Full" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21620,4 +21621,6692 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AO52"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>SHA_miles</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>state_tot_lane_miles</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>SHA_ratio</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>pct_urban_lane_miles</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>urban_lm_index</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>capital_disbursement</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>maintenance_disbursement</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>admin_disbursement</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>other_disbursement</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>rural_interstate_above_170</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>rural_interstate_total</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>rural_OPA_above_220</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>rural_OPA_total</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>urban_interstate_above_170</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>urban_interstate_total</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>urban_OPA_above_220</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>urban_OPA_total</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>rural_fatality_interstate_OFE_OPA</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>urban_fatality_interstate_OFE_OPA</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>other_fatality</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>rural_VMT_interstate_OFE_OPA</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>urban_VMT_interstate_OFE_OPA</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>other_VMT</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>total_bridges</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>total_poor_bridges</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>state_tot_congestion_hours</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>state_tot_commuters</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>capital_disbursement_perlm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>maintenance_disbursement_perlm</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>admin_disbursement_perlm</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>other_disbursement_perlm</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>rural_interstate_poor_percent</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>urban_interstate_poor_percent</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>rural_OPA_poor_percent</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>urban_OPA_poor_percent</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>state_avg_congestion_hours</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>poor_bridges_percent</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>rural_fatalities_per_100m_VMT</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>urban_fatalities_per_100m_VMT</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>other_fatalities_per_100m_VMT</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Alabama</t>
+        </is>
+      </c>
+      <c r="B2">
+        <v>10962.392</v>
+      </c>
+      <c r="C2">
+        <v>29843.076</v>
+      </c>
+      <c r="D2">
+        <v>2.722314254042366</v>
+      </c>
+      <c r="E2">
+        <v>0.3170098149399881</v>
+      </c>
+      <c r="F2">
+        <v>1.130501213603269</v>
+      </c>
+      <c r="G2">
+        <v>1266049000</v>
+      </c>
+      <c r="H2">
+        <v>34385000</v>
+      </c>
+      <c r="I2">
+        <v>420120000</v>
+      </c>
+      <c r="J2">
+        <v>1428197000</v>
+      </c>
+      <c r="K2">
+        <v>10.271</v>
+      </c>
+      <c r="L2">
+        <v>570.321</v>
+      </c>
+      <c r="M2">
+        <v>5.019</v>
+      </c>
+      <c r="N2">
+        <v>2022.434</v>
+      </c>
+      <c r="O2">
+        <v>16.744</v>
+      </c>
+      <c r="P2">
+        <v>432.493</v>
+      </c>
+      <c r="Q2">
+        <v>12.093</v>
+      </c>
+      <c r="R2">
+        <v>1162.894</v>
+      </c>
+      <c r="S2">
+        <v>184</v>
+      </c>
+      <c r="T2">
+        <v>202</v>
+      </c>
+      <c r="U2">
+        <v>600</v>
+      </c>
+      <c r="V2">
+        <v>12492.79469</v>
+      </c>
+      <c r="W2">
+        <v>19462.9714</v>
+      </c>
+      <c r="X2">
+        <v>39674.77306</v>
+      </c>
+      <c r="Y2">
+        <v>16162</v>
+      </c>
+      <c r="Z2">
+        <v>575</v>
+      </c>
+      <c r="AA2">
+        <v>20205638.9051532</v>
+      </c>
+      <c r="AB2">
+        <v>1498977.686746575</v>
+      </c>
+      <c r="AC2">
+        <v>42423.54239891357</v>
+      </c>
+      <c r="AD2">
+        <v>1152.193560744207</v>
+      </c>
+      <c r="AE2">
+        <v>14077.63730521612</v>
+      </c>
+      <c r="AF2">
+        <v>47856.89652098865</v>
+      </c>
+      <c r="AG2">
+        <v>1.800915624709594</v>
+      </c>
+      <c r="AH2">
+        <v>3.871507746946194</v>
+      </c>
+      <c r="AI2">
+        <v>0.248166318406435</v>
+      </c>
+      <c r="AJ2">
+        <v>1.039905614785182</v>
+      </c>
+      <c r="AK2">
+        <v>13.47961286135493</v>
+      </c>
+      <c r="AL2">
+        <v>3.557728003959906</v>
+      </c>
+      <c r="AM2">
+        <v>1.472848986682579</v>
+      </c>
+      <c r="AN2">
+        <v>1.037868246572052</v>
+      </c>
+      <c r="AO2">
+        <v>1.512295984888489</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="B3">
+        <v>5682.737</v>
+      </c>
+      <c r="C3">
+        <v>11858.371</v>
+      </c>
+      <c r="D3">
+        <v>2.086735845772908</v>
+      </c>
+      <c r="E3">
+        <v>0.1498568395271155</v>
+      </c>
+      <c r="F3">
+        <v>0.5344103903667005</v>
+      </c>
+      <c r="G3">
+        <v>702933000</v>
+      </c>
+      <c r="H3">
+        <v>217887000</v>
+      </c>
+      <c r="I3">
+        <v>43674000</v>
+      </c>
+      <c r="J3">
+        <v>92457000</v>
+      </c>
+      <c r="K3">
+        <v>93.104</v>
+      </c>
+      <c r="L3">
+        <v>1000.836</v>
+      </c>
+      <c r="M3">
+        <v>62.487</v>
+      </c>
+      <c r="N3">
+        <v>521.099</v>
+      </c>
+      <c r="O3">
+        <v>0.751</v>
+      </c>
+      <c r="P3">
+        <v>78.718</v>
+      </c>
+      <c r="Q3">
+        <v>9.255000000000001</v>
+      </c>
+      <c r="R3">
+        <v>138.073</v>
+      </c>
+      <c r="S3">
+        <v>30</v>
+      </c>
+      <c r="T3">
+        <v>30</v>
+      </c>
+      <c r="U3">
+        <v>20</v>
+      </c>
+      <c r="V3">
+        <v>1118.26821</v>
+      </c>
+      <c r="W3">
+        <v>1602.98918</v>
+      </c>
+      <c r="X3">
+        <v>2756.95203</v>
+      </c>
+      <c r="Y3">
+        <v>1626</v>
+      </c>
+      <c r="Z3">
+        <v>126</v>
+      </c>
+      <c r="AA3">
+        <v>1908035.200253221</v>
+      </c>
+      <c r="AB3">
+        <v>187845.3636363636</v>
+      </c>
+      <c r="AC3">
+        <v>59277.36617449395</v>
+      </c>
+      <c r="AD3">
+        <v>18374.10888898652</v>
+      </c>
+      <c r="AE3">
+        <v>3682.967921985237</v>
+      </c>
+      <c r="AF3">
+        <v>7796.770736891265</v>
+      </c>
+      <c r="AG3">
+        <v>9.302623007166009</v>
+      </c>
+      <c r="AH3">
+        <v>0.9540384664244518</v>
+      </c>
+      <c r="AI3">
+        <v>11.99138743309812</v>
+      </c>
+      <c r="AJ3">
+        <v>6.702975961991122</v>
+      </c>
+      <c r="AK3">
+        <v>10.15747827530548</v>
+      </c>
+      <c r="AL3">
+        <v>7.749077490774908</v>
+      </c>
+      <c r="AM3">
+        <v>2.68271955973782</v>
+      </c>
+      <c r="AN3">
+        <v>1.871503586817723</v>
+      </c>
+      <c r="AO3">
+        <v>0.7254388100470504</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Arizona</t>
+        </is>
+      </c>
+      <c r="B4">
+        <v>6863.532999999999</v>
+      </c>
+      <c r="C4">
+        <v>20050.434</v>
+      </c>
+      <c r="D4">
+        <v>2.921299278374563</v>
+      </c>
+      <c r="E4">
+        <v>0.2963756295749009</v>
+      </c>
+      <c r="F4">
+        <v>1.056916830730576</v>
+      </c>
+      <c r="G4">
+        <v>907115000</v>
+      </c>
+      <c r="H4">
+        <v>150046000</v>
+      </c>
+      <c r="I4">
+        <v>269525000</v>
+      </c>
+      <c r="J4">
+        <v>457728000</v>
+      </c>
+      <c r="K4">
+        <v>30.556</v>
+      </c>
+      <c r="L4">
+        <v>907.3390000000001</v>
+      </c>
+      <c r="M4">
+        <v>13.405</v>
+      </c>
+      <c r="N4">
+        <v>1243.241</v>
+      </c>
+      <c r="O4">
+        <v>3.544</v>
+      </c>
+      <c r="P4">
+        <v>241.12</v>
+      </c>
+      <c r="Q4">
+        <v>47.46</v>
+      </c>
+      <c r="R4">
+        <v>672.909</v>
+      </c>
+      <c r="S4">
+        <v>214</v>
+      </c>
+      <c r="T4">
+        <v>330</v>
+      </c>
+      <c r="U4">
+        <v>690</v>
+      </c>
+      <c r="V4">
+        <v>11901.24458</v>
+      </c>
+      <c r="W4">
+        <v>26550.15419</v>
+      </c>
+      <c r="X4">
+        <v>37707.91279</v>
+      </c>
+      <c r="Y4">
+        <v>8497</v>
+      </c>
+      <c r="Z4">
+        <v>107</v>
+      </c>
+      <c r="AA4">
+        <v>53818958.26511038</v>
+      </c>
+      <c r="AB4">
+        <v>2304383.636363636</v>
+      </c>
+      <c r="AC4">
+        <v>45241.66409565</v>
+      </c>
+      <c r="AD4">
+        <v>7483.429036997403</v>
+      </c>
+      <c r="AE4">
+        <v>13442.35241990273</v>
+      </c>
+      <c r="AF4">
+        <v>22828.83253300153</v>
+      </c>
+      <c r="AG4">
+        <v>3.367649797925582</v>
+      </c>
+      <c r="AH4">
+        <v>1.469807564698076</v>
+      </c>
+      <c r="AI4">
+        <v>1.078230206371894</v>
+      </c>
+      <c r="AJ4">
+        <v>7.052959612666794</v>
+      </c>
+      <c r="AK4">
+        <v>23.35503403853265</v>
+      </c>
+      <c r="AL4">
+        <v>1.259267976933035</v>
+      </c>
+      <c r="AM4">
+        <v>1.79813126737708</v>
+      </c>
+      <c r="AN4">
+        <v>1.242930634746721</v>
+      </c>
+      <c r="AO4">
+        <v>1.829854661653364</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="B5">
+        <v>16435.945</v>
+      </c>
+      <c r="C5">
+        <v>38159.593</v>
+      </c>
+      <c r="D5">
+        <v>2.321715788170379</v>
+      </c>
+      <c r="E5">
+        <v>0.1861831702450286</v>
+      </c>
+      <c r="F5">
+        <v>0.6639551521594186</v>
+      </c>
+      <c r="G5">
+        <v>1400824000</v>
+      </c>
+      <c r="H5">
+        <v>221948000</v>
+      </c>
+      <c r="I5">
+        <v>41327000</v>
+      </c>
+      <c r="J5">
+        <v>303089000</v>
+      </c>
+      <c r="K5">
+        <v>13.2</v>
+      </c>
+      <c r="L5">
+        <v>445.172</v>
+      </c>
+      <c r="M5">
+        <v>28.278</v>
+      </c>
+      <c r="N5">
+        <v>1876.381</v>
+      </c>
+      <c r="O5">
+        <v>19.485</v>
+      </c>
+      <c r="P5">
+        <v>322.602</v>
+      </c>
+      <c r="Q5">
+        <v>64.163</v>
+      </c>
+      <c r="R5">
+        <v>617.963</v>
+      </c>
+      <c r="S5">
+        <v>153</v>
+      </c>
+      <c r="T5">
+        <v>166</v>
+      </c>
+      <c r="U5">
+        <v>320</v>
+      </c>
+      <c r="V5">
+        <v>8765.989089999999</v>
+      </c>
+      <c r="W5">
+        <v>10928.41279</v>
+      </c>
+      <c r="X5">
+        <v>18836.07068</v>
+      </c>
+      <c r="Y5">
+        <v>12955</v>
+      </c>
+      <c r="Z5">
+        <v>674</v>
+      </c>
+      <c r="AA5">
+        <v>5274684.483503148</v>
+      </c>
+      <c r="AB5">
+        <v>761287.6127722721</v>
+      </c>
+      <c r="AC5">
+        <v>36709.61584941432</v>
+      </c>
+      <c r="AD5">
+        <v>5816.309413991916</v>
+      </c>
+      <c r="AE5">
+        <v>1083.004213383513</v>
+      </c>
+      <c r="AF5">
+        <v>7942.66857091479</v>
+      </c>
+      <c r="AG5">
+        <v>2.965146055906481</v>
+      </c>
+      <c r="AH5">
+        <v>6.039950155299719</v>
+      </c>
+      <c r="AI5">
+        <v>1.507050007434524</v>
+      </c>
+      <c r="AJ5">
+        <v>10.38298409451698</v>
+      </c>
+      <c r="AK5">
+        <v>6.928635636530436</v>
+      </c>
+      <c r="AL5">
+        <v>5.202624469316866</v>
+      </c>
+      <c r="AM5">
+        <v>1.745382049066639</v>
+      </c>
+      <c r="AN5">
+        <v>1.518976297746528</v>
+      </c>
+      <c r="AO5">
+        <v>1.698868120832513</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>15016.58</v>
+      </c>
+      <c r="C6">
+        <v>52016.195</v>
+      </c>
+      <c r="D6">
+        <v>3.463917549801619</v>
+      </c>
+      <c r="E6">
+        <v>0.4761190240847106</v>
+      </c>
+      <c r="F6">
+        <v>1.697906844459262</v>
+      </c>
+      <c r="G6">
+        <v>5487338000</v>
+      </c>
+      <c r="H6">
+        <v>2253779000</v>
+      </c>
+      <c r="I6">
+        <v>677815000</v>
+      </c>
+      <c r="J6">
+        <v>3213724000</v>
+      </c>
+      <c r="K6">
+        <v>59.154</v>
+      </c>
+      <c r="L6">
+        <v>1208.852</v>
+      </c>
+      <c r="M6">
+        <v>64.083</v>
+      </c>
+      <c r="N6">
+        <v>3342.014</v>
+      </c>
+      <c r="O6">
+        <v>116.161</v>
+      </c>
+      <c r="P6">
+        <v>1237.316</v>
+      </c>
+      <c r="Q6">
+        <v>1917.983</v>
+      </c>
+      <c r="R6">
+        <v>6153.884</v>
+      </c>
+      <c r="S6">
+        <v>450</v>
+      </c>
+      <c r="T6">
+        <v>1940</v>
+      </c>
+      <c r="U6">
+        <v>2028</v>
+      </c>
+      <c r="V6">
+        <v>35448.43201</v>
+      </c>
+      <c r="W6">
+        <v>178118.71365</v>
+      </c>
+      <c r="X6">
+        <v>101676.42693</v>
+      </c>
+      <c r="Y6">
+        <v>25810</v>
+      </c>
+      <c r="Z6">
+        <v>1547</v>
+      </c>
+      <c r="AA6">
+        <v>769617194.701757</v>
+      </c>
+      <c r="AB6">
+        <v>12769385.72727273</v>
+      </c>
+      <c r="AC6">
+        <v>105492.8758245389</v>
+      </c>
+      <c r="AD6">
+        <v>43328.40954629611</v>
+      </c>
+      <c r="AE6">
+        <v>13030.84548956339</v>
+      </c>
+      <c r="AF6">
+        <v>61783.14273083604</v>
+      </c>
+      <c r="AG6">
+        <v>4.893402997223812</v>
+      </c>
+      <c r="AH6">
+        <v>9.388143368387704</v>
+      </c>
+      <c r="AI6">
+        <v>1.917496455729988</v>
+      </c>
+      <c r="AJ6">
+        <v>31.16703207275275</v>
+      </c>
+      <c r="AK6">
+        <v>60.27049469247499</v>
+      </c>
+      <c r="AL6">
+        <v>5.993800852382797</v>
+      </c>
+      <c r="AM6">
+        <v>1.269449661054274</v>
+      </c>
+      <c r="AN6">
+        <v>1.089161245466922</v>
+      </c>
+      <c r="AO6">
+        <v>1.994562615183354</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>9029.424999999999</v>
+      </c>
+      <c r="C7">
+        <v>23186.718</v>
+      </c>
+      <c r="D7">
+        <v>2.567906372775675</v>
+      </c>
+      <c r="E7">
+        <v>0.258020345958406</v>
+      </c>
+      <c r="F7">
+        <v>0.9201365399223762</v>
+      </c>
+      <c r="G7">
+        <v>1392181000</v>
+      </c>
+      <c r="H7">
+        <v>611031000</v>
+      </c>
+      <c r="I7">
+        <v>147662000</v>
+      </c>
+      <c r="J7">
+        <v>266011000</v>
+      </c>
+      <c r="K7">
+        <v>46.06</v>
+      </c>
+      <c r="L7">
+        <v>648.121</v>
+      </c>
+      <c r="M7">
+        <v>38.916</v>
+      </c>
+      <c r="N7">
+        <v>2568.707</v>
+      </c>
+      <c r="O7">
+        <v>24.24</v>
+      </c>
+      <c r="P7">
+        <v>303.728</v>
+      </c>
+      <c r="Q7">
+        <v>129.026</v>
+      </c>
+      <c r="R7">
+        <v>1067.773</v>
+      </c>
+      <c r="S7">
+        <v>147</v>
+      </c>
+      <c r="T7">
+        <v>310</v>
+      </c>
+      <c r="U7">
+        <v>305</v>
+      </c>
+      <c r="V7">
+        <v>10130.98419</v>
+      </c>
+      <c r="W7">
+        <v>24320.94021</v>
+      </c>
+      <c r="X7">
+        <v>19483.36215</v>
+      </c>
+      <c r="Y7">
+        <v>8917</v>
+      </c>
+      <c r="Z7">
+        <v>452</v>
+      </c>
+      <c r="AA7">
+        <v>68206849.16968459</v>
+      </c>
+      <c r="AB7">
+        <v>1883450.909090908</v>
+      </c>
+      <c r="AC7">
+        <v>60042.1758698234</v>
+      </c>
+      <c r="AD7">
+        <v>26352.62998411418</v>
+      </c>
+      <c r="AE7">
+        <v>6368.387281028734</v>
+      </c>
+      <c r="AF7">
+        <v>11472.55941957805</v>
+      </c>
+      <c r="AG7">
+        <v>7.106697669108083</v>
+      </c>
+      <c r="AH7">
+        <v>7.980824948638254</v>
+      </c>
+      <c r="AI7">
+        <v>1.515003462831689</v>
+      </c>
+      <c r="AJ7">
+        <v>12.08365448461424</v>
+      </c>
+      <c r="AK7">
+        <v>36.2137652967054</v>
+      </c>
+      <c r="AL7">
+        <v>5.068969384322082</v>
+      </c>
+      <c r="AM7">
+        <v>1.450994269096772</v>
+      </c>
+      <c r="AN7">
+        <v>1.274621775816618</v>
+      </c>
+      <c r="AO7">
+        <v>1.565438232127713</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>3715</v>
+      </c>
+      <c r="C8">
+        <v>9825.18</v>
+      </c>
+      <c r="D8">
+        <v>2.644732166890983</v>
+      </c>
+      <c r="E8">
+        <v>0.7439711028194902</v>
+      </c>
+      <c r="F8">
+        <v>2.653104714699178</v>
+      </c>
+      <c r="G8">
+        <v>1023676000</v>
+      </c>
+      <c r="H8">
+        <v>284943000</v>
+      </c>
+      <c r="I8">
+        <v>81358000</v>
+      </c>
+      <c r="J8">
+        <v>925761000</v>
+      </c>
+      <c r="K8">
+        <v>0.11</v>
+      </c>
+      <c r="L8">
+        <v>28.74</v>
+      </c>
+      <c r="M8">
+        <v>1.67</v>
+      </c>
+      <c r="N8">
+        <v>122.07</v>
+      </c>
+      <c r="O8">
+        <v>5.82</v>
+      </c>
+      <c r="P8">
+        <v>317.6</v>
+      </c>
+      <c r="Q8">
+        <v>67.14</v>
+      </c>
+      <c r="R8">
+        <v>710.0700000000001</v>
+      </c>
+      <c r="S8">
+        <v>16</v>
+      </c>
+      <c r="T8">
+        <v>172</v>
+      </c>
+      <c r="U8">
+        <v>167</v>
+      </c>
+      <c r="V8">
+        <v>1167.52661</v>
+      </c>
+      <c r="W8">
+        <v>17070.06615</v>
+      </c>
+      <c r="X8">
+        <v>11428.72158</v>
+      </c>
+      <c r="Y8">
+        <v>4353</v>
+      </c>
+      <c r="Z8">
+        <v>225</v>
+      </c>
+      <c r="AA8">
+        <v>36477756.39170325</v>
+      </c>
+      <c r="AB8">
+        <v>1276259.837986254</v>
+      </c>
+      <c r="AC8">
+        <v>104189.0326691216</v>
+      </c>
+      <c r="AD8">
+        <v>29001.30073952844</v>
+      </c>
+      <c r="AE8">
+        <v>8280.560763263369</v>
+      </c>
+      <c r="AF8">
+        <v>94223.31193932325</v>
+      </c>
+      <c r="AG8">
+        <v>0.3827418232428671</v>
+      </c>
+      <c r="AH8">
+        <v>1.832493702770781</v>
+      </c>
+      <c r="AI8">
+        <v>1.368067502252806</v>
+      </c>
+      <c r="AJ8">
+        <v>9.455405805061472</v>
+      </c>
+      <c r="AK8">
+        <v>28.58176313787298</v>
+      </c>
+      <c r="AL8">
+        <v>5.168849069607168</v>
+      </c>
+      <c r="AM8">
+        <v>1.370418443824591</v>
+      </c>
+      <c r="AN8">
+        <v>1.00761179534152</v>
+      </c>
+      <c r="AO8">
+        <v>1.461230801984416</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>5485.84</v>
+      </c>
+      <c r="C9">
+        <v>12035.37</v>
+      </c>
+      <c r="D9">
+        <v>2.193897379435055</v>
+      </c>
+      <c r="E9">
+        <v>0.5324373077022143</v>
+      </c>
+      <c r="F9">
+        <v>1.89874569858021</v>
+      </c>
+      <c r="G9">
+        <v>499530000</v>
+      </c>
+      <c r="H9">
+        <v>610259000</v>
+      </c>
+      <c r="I9">
+        <v>348434000</v>
+      </c>
+      <c r="J9">
+        <v>252623000</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0.67</v>
+      </c>
+      <c r="N9">
+        <v>99.26000000000001</v>
+      </c>
+      <c r="O9">
+        <v>3.72</v>
+      </c>
+      <c r="P9">
+        <v>39.77</v>
+      </c>
+      <c r="Q9">
+        <v>13.31</v>
+      </c>
+      <c r="R9">
+        <v>211.24</v>
+      </c>
+      <c r="S9">
+        <v>34</v>
+      </c>
+      <c r="T9">
+        <v>51</v>
+      </c>
+      <c r="U9">
+        <v>77</v>
+      </c>
+      <c r="V9">
+        <v>1137.3758</v>
+      </c>
+      <c r="W9">
+        <v>4263.65329</v>
+      </c>
+      <c r="X9">
+        <v>4471.370339999999</v>
+      </c>
+      <c r="Y9">
+        <v>872</v>
+      </c>
+      <c r="Z9">
+        <v>14</v>
+      </c>
+      <c r="AA9">
+        <v>29033764.67360982</v>
+      </c>
+      <c r="AB9">
+        <v>350696.6566023649</v>
+      </c>
+      <c r="AC9">
+        <v>41505.16353049387</v>
+      </c>
+      <c r="AD9">
+        <v>50705.46231648881</v>
+      </c>
+      <c r="AE9">
+        <v>28950.83408320641</v>
+      </c>
+      <c r="AF9">
+        <v>20990.0484987167</v>
+      </c>
+      <c r="AH9">
+        <v>9.353784259492079</v>
+      </c>
+      <c r="AI9">
+        <v>0.6749949627241587</v>
+      </c>
+      <c r="AJ9">
+        <v>6.300889982957774</v>
+      </c>
+      <c r="AK9">
+        <v>82.78882654569918</v>
+      </c>
+      <c r="AL9">
+        <v>1.605504587155963</v>
+      </c>
+      <c r="AM9">
+        <v>2.989337385233623</v>
+      </c>
+      <c r="AN9">
+        <v>1.196157298240355</v>
+      </c>
+      <c r="AO9">
+        <v>1.722067154920565</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>12157.566</v>
+      </c>
+      <c r="C10">
+        <v>45438.773</v>
+      </c>
+      <c r="D10">
+        <v>3.73748931323918</v>
+      </c>
+      <c r="E10">
+        <v>0.6413355395842225</v>
+      </c>
+      <c r="F10">
+        <v>2.287091981565694</v>
+      </c>
+      <c r="G10">
+        <v>6504653000</v>
+      </c>
+      <c r="H10">
+        <v>1437379000</v>
+      </c>
+      <c r="I10">
+        <v>453911000</v>
+      </c>
+      <c r="J10">
+        <v>2590205000</v>
+      </c>
+      <c r="K10">
+        <v>1.69</v>
+      </c>
+      <c r="L10">
+        <v>714.667</v>
+      </c>
+      <c r="M10">
+        <v>6.724</v>
+      </c>
+      <c r="N10">
+        <v>2625.087</v>
+      </c>
+      <c r="O10">
+        <v>7.627000000000001</v>
+      </c>
+      <c r="P10">
+        <v>749.977</v>
+      </c>
+      <c r="Q10">
+        <v>104.183</v>
+      </c>
+      <c r="R10">
+        <v>3950.148</v>
+      </c>
+      <c r="S10">
+        <v>384</v>
+      </c>
+      <c r="T10">
+        <v>1481</v>
+      </c>
+      <c r="U10">
+        <v>1653</v>
+      </c>
+      <c r="V10">
+        <v>24146.11898</v>
+      </c>
+      <c r="W10">
+        <v>94637.51416999999</v>
+      </c>
+      <c r="X10">
+        <v>108973.50431</v>
+      </c>
+      <c r="Y10">
+        <v>12740</v>
+      </c>
+      <c r="Z10">
+        <v>455</v>
+      </c>
+      <c r="AA10">
+        <v>334611289.3243703</v>
+      </c>
+      <c r="AB10">
+        <v>7443904.797128422</v>
+      </c>
+      <c r="AC10">
+        <v>143152.0388985856</v>
+      </c>
+      <c r="AD10">
+        <v>31633.31457035603</v>
+      </c>
+      <c r="AE10">
+        <v>9989.508299442856</v>
+      </c>
+      <c r="AF10">
+        <v>57004.29014665515</v>
+      </c>
+      <c r="AG10">
+        <v>0.2364737703014131</v>
+      </c>
+      <c r="AH10">
+        <v>1.016964520245288</v>
+      </c>
+      <c r="AI10">
+        <v>0.2561438916119733</v>
+      </c>
+      <c r="AJ10">
+        <v>2.637445483055318</v>
+      </c>
+      <c r="AK10">
+        <v>44.95104363148904</v>
+      </c>
+      <c r="AL10">
+        <v>3.571428571428571</v>
+      </c>
+      <c r="AM10">
+        <v>1.59031768342591</v>
+      </c>
+      <c r="AN10">
+        <v>1.564918534672877</v>
+      </c>
+      <c r="AO10">
+        <v>1.516882484844815</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Georgia</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>17905.601</v>
+      </c>
+      <c r="C11">
+        <v>49569.79</v>
+      </c>
+      <c r="D11">
+        <v>2.768395766218626</v>
+      </c>
+      <c r="E11">
+        <v>0.3825537893140157</v>
+      </c>
+      <c r="F11">
+        <v>1.364240167673972</v>
+      </c>
+      <c r="G11">
+        <v>1803146000</v>
+      </c>
+      <c r="H11">
+        <v>645070000</v>
+      </c>
+      <c r="I11">
+        <v>383884000</v>
+      </c>
+      <c r="J11">
+        <v>1209041000</v>
+      </c>
+      <c r="K11">
+        <v>3.187</v>
+      </c>
+      <c r="L11">
+        <v>538.249</v>
+      </c>
+      <c r="M11">
+        <v>5.02</v>
+      </c>
+      <c r="N11">
+        <v>2412.196</v>
+      </c>
+      <c r="O11">
+        <v>10.864</v>
+      </c>
+      <c r="P11">
+        <v>708.814</v>
+      </c>
+      <c r="Q11">
+        <v>45.605</v>
+      </c>
+      <c r="R11">
+        <v>2284.986</v>
+      </c>
+      <c r="S11">
+        <v>181</v>
+      </c>
+      <c r="T11">
+        <v>577</v>
+      </c>
+      <c r="U11">
+        <v>1038</v>
+      </c>
+      <c r="V11">
+        <v>14998.43489</v>
+      </c>
+      <c r="W11">
+        <v>46381.97059</v>
+      </c>
+      <c r="X11">
+        <v>67490.65022000001</v>
+      </c>
+      <c r="Y11">
+        <v>15034</v>
+      </c>
+      <c r="Z11">
+        <v>293</v>
+      </c>
+      <c r="AA11">
+        <v>175328710.1414601</v>
+      </c>
+      <c r="AB11">
+        <v>3257225.023098981</v>
+      </c>
+      <c r="AC11">
+        <v>36375.9055666768</v>
+      </c>
+      <c r="AD11">
+        <v>13013.36963501358</v>
+      </c>
+      <c r="AE11">
+        <v>7744.313623277403</v>
+      </c>
+      <c r="AF11">
+        <v>24390.68230872069</v>
+      </c>
+      <c r="AG11">
+        <v>0.5921051409291982</v>
+      </c>
+      <c r="AH11">
+        <v>1.532701103533508</v>
+      </c>
+      <c r="AI11">
+        <v>0.2081091254607834</v>
+      </c>
+      <c r="AJ11">
+        <v>1.995854679197159</v>
+      </c>
+      <c r="AK11">
+        <v>53.82763207886978</v>
+      </c>
+      <c r="AL11">
+        <v>1.948915790874019</v>
+      </c>
+      <c r="AM11">
+        <v>1.206792584209431</v>
+      </c>
+      <c r="AN11">
+        <v>1.244017864399237</v>
+      </c>
+      <c r="AO11">
+        <v>1.537990812973975</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Hawaii</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>952.3140000000001</v>
+      </c>
+      <c r="C12">
+        <v>2490.973</v>
+      </c>
+      <c r="D12">
+        <v>2.615705534099047</v>
+      </c>
+      <c r="E12">
+        <v>0.6168766180926089</v>
+      </c>
+      <c r="F12">
+        <v>2.199868056227828</v>
+      </c>
+      <c r="G12">
+        <v>223540000</v>
+      </c>
+      <c r="H12">
+        <v>47198000</v>
+      </c>
+      <c r="I12">
+        <v>25043000</v>
+      </c>
+      <c r="J12">
+        <v>92992000</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>3.121</v>
+      </c>
+      <c r="N12">
+        <v>77.65000000000001</v>
+      </c>
+      <c r="O12">
+        <v>10.725</v>
+      </c>
+      <c r="P12">
+        <v>54.852</v>
+      </c>
+      <c r="Q12">
+        <v>37.951</v>
+      </c>
+      <c r="R12">
+        <v>266.901</v>
+      </c>
+      <c r="S12">
+        <v>13</v>
+      </c>
+      <c r="T12">
+        <v>67</v>
+      </c>
+      <c r="U12">
+        <v>35</v>
+      </c>
+      <c r="V12">
+        <v>321.85252</v>
+      </c>
+      <c r="W12">
+        <v>4330.03586</v>
+      </c>
+      <c r="X12">
+        <v>5637.18732</v>
+      </c>
+      <c r="Y12">
+        <v>1177</v>
+      </c>
+      <c r="Z12">
+        <v>74</v>
+      </c>
+      <c r="AA12">
+        <v>6008137.315173937</v>
+      </c>
+      <c r="AB12">
+        <v>404433.7272727273</v>
+      </c>
+      <c r="AC12">
+        <v>89740.03331228399</v>
+      </c>
+      <c r="AD12">
+        <v>18947.61605204071</v>
+      </c>
+      <c r="AE12">
+        <v>10053.50118206821</v>
+      </c>
+      <c r="AF12">
+        <v>37331.59693019555</v>
+      </c>
+      <c r="AH12">
+        <v>19.55261430759134</v>
+      </c>
+      <c r="AI12">
+        <v>4.019317450096587</v>
+      </c>
+      <c r="AJ12">
+        <v>14.21912993956561</v>
+      </c>
+      <c r="AK12">
+        <v>14.85567822369668</v>
+      </c>
+      <c r="AL12">
+        <v>6.287170773152082</v>
+      </c>
+      <c r="AM12">
+        <v>4.039117046528018</v>
+      </c>
+      <c r="AN12">
+        <v>1.5473312962355</v>
+      </c>
+      <c r="AO12">
+        <v>0.6208770085717144</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>4960.684</v>
+      </c>
+      <c r="C13">
+        <v>12223.031</v>
+      </c>
+      <c r="D13">
+        <v>2.463980975204226</v>
+      </c>
+      <c r="E13">
+        <v>0.1142191327175723</v>
+      </c>
+      <c r="F13">
+        <v>0.4073213574739712</v>
+      </c>
+      <c r="G13">
+        <v>726996000</v>
+      </c>
+      <c r="H13">
+        <v>123728000</v>
+      </c>
+      <c r="I13">
+        <v>37044000</v>
+      </c>
+      <c r="J13">
+        <v>120579000</v>
+      </c>
+      <c r="K13">
+        <v>5.622</v>
+      </c>
+      <c r="L13">
+        <v>515.9059999999999</v>
+      </c>
+      <c r="M13">
+        <v>7.441</v>
+      </c>
+      <c r="N13">
+        <v>1604.405</v>
+      </c>
+      <c r="O13">
+        <v>0.8059999999999999</v>
+      </c>
+      <c r="P13">
+        <v>93.46899999999999</v>
+      </c>
+      <c r="Q13">
+        <v>10.783</v>
+      </c>
+      <c r="R13">
+        <v>220.555</v>
+      </c>
+      <c r="S13">
+        <v>68</v>
+      </c>
+      <c r="T13">
+        <v>28</v>
+      </c>
+      <c r="U13">
+        <v>119</v>
+      </c>
+      <c r="V13">
+        <v>5812.78358</v>
+      </c>
+      <c r="W13">
+        <v>4339.72879</v>
+      </c>
+      <c r="X13">
+        <v>9004.89149</v>
+      </c>
+      <c r="Y13">
+        <v>4579</v>
+      </c>
+      <c r="Z13">
+        <v>234</v>
+      </c>
+      <c r="AA13">
+        <v>3787926.342579184</v>
+      </c>
+      <c r="AB13">
+        <v>508442.0455673349</v>
+      </c>
+      <c r="AC13">
+        <v>59477.55511705729</v>
+      </c>
+      <c r="AD13">
+        <v>10122.53016457211</v>
+      </c>
+      <c r="AE13">
+        <v>3030.672179429145</v>
+      </c>
+      <c r="AF13">
+        <v>9864.90175800094</v>
+      </c>
+      <c r="AG13">
+        <v>1.089733401045927</v>
+      </c>
+      <c r="AH13">
+        <v>0.8623179877820454</v>
+      </c>
+      <c r="AI13">
+        <v>0.463785640159436</v>
+      </c>
+      <c r="AJ13">
+        <v>4.889029947178708</v>
+      </c>
+      <c r="AK13">
+        <v>7.450065106933677</v>
+      </c>
+      <c r="AL13">
+        <v>5.110286088665648</v>
+      </c>
+      <c r="AM13">
+        <v>1.169835399239137</v>
+      </c>
+      <c r="AN13">
+        <v>0.6452016094766143</v>
+      </c>
+      <c r="AO13">
+        <v>1.32150398627402</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>15890.22</v>
+      </c>
+      <c r="C14">
+        <v>42212.46</v>
+      </c>
+      <c r="D14">
+        <v>2.656505699732288</v>
+      </c>
+      <c r="E14">
+        <v>0.431261527994341</v>
+      </c>
+      <c r="F14">
+        <v>1.537938757102198</v>
+      </c>
+      <c r="G14">
+        <v>4153116000</v>
+      </c>
+      <c r="H14">
+        <v>817198000</v>
+      </c>
+      <c r="I14">
+        <v>378443000</v>
+      </c>
+      <c r="J14">
+        <v>1369206000</v>
+      </c>
+      <c r="K14">
+        <v>19.13</v>
+      </c>
+      <c r="L14">
+        <v>1247.07</v>
+      </c>
+      <c r="M14">
+        <v>49.49</v>
+      </c>
+      <c r="N14">
+        <v>2362.58</v>
+      </c>
+      <c r="O14">
+        <v>44.63999999999999</v>
+      </c>
+      <c r="P14">
+        <v>938.1</v>
+      </c>
+      <c r="Q14">
+        <v>333.29</v>
+      </c>
+      <c r="R14">
+        <v>2885.18</v>
+      </c>
+      <c r="S14">
+        <v>141</v>
+      </c>
+      <c r="T14">
+        <v>423</v>
+      </c>
+      <c r="U14">
+        <v>695</v>
+      </c>
+      <c r="V14">
+        <v>13529.54934</v>
+      </c>
+      <c r="W14">
+        <v>44463.79168</v>
+      </c>
+      <c r="X14">
+        <v>45758.84587</v>
+      </c>
+      <c r="Y14">
+        <v>26873</v>
+      </c>
+      <c r="Z14">
+        <v>2423</v>
+      </c>
+      <c r="AA14">
+        <v>253840238.1117491</v>
+      </c>
+      <c r="AB14">
+        <v>3929310.32470964</v>
+      </c>
+      <c r="AC14">
+        <v>98386.02156803939</v>
+      </c>
+      <c r="AD14">
+        <v>19359.16551653232</v>
+      </c>
+      <c r="AE14">
+        <v>8965.196532019219</v>
+      </c>
+      <c r="AF14">
+        <v>32436.06271702715</v>
+      </c>
+      <c r="AG14">
+        <v>1.533995685887721</v>
+      </c>
+      <c r="AH14">
+        <v>4.758554525103933</v>
+      </c>
+      <c r="AI14">
+        <v>2.094743881688663</v>
+      </c>
+      <c r="AJ14">
+        <v>11.55179226252782</v>
+      </c>
+      <c r="AK14">
+        <v>64.6017283276059</v>
+      </c>
+      <c r="AL14">
+        <v>9.016484947717039</v>
+      </c>
+      <c r="AM14">
+        <v>1.042163315692524</v>
+      </c>
+      <c r="AN14">
+        <v>0.9513358713181159</v>
+      </c>
+      <c r="AO14">
+        <v>1.518832013321493</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>11077.973</v>
+      </c>
+      <c r="C15">
+        <v>28595.774</v>
+      </c>
+      <c r="D15">
+        <v>2.581318261021218</v>
+      </c>
+      <c r="E15">
+        <v>0.2747851133527632</v>
+      </c>
+      <c r="F15">
+        <v>0.9799220386416673</v>
+      </c>
+      <c r="G15">
+        <v>1997211000</v>
+      </c>
+      <c r="H15">
+        <v>1024810000</v>
+      </c>
+      <c r="I15">
+        <v>133564000</v>
+      </c>
+      <c r="J15">
+        <v>289527000</v>
+      </c>
+      <c r="K15">
+        <v>15.129</v>
+      </c>
+      <c r="L15">
+        <v>811.778</v>
+      </c>
+      <c r="M15">
+        <v>4.13</v>
+      </c>
+      <c r="N15">
+        <v>1906.909</v>
+      </c>
+      <c r="O15">
+        <v>14.383</v>
+      </c>
+      <c r="P15">
+        <v>492.486</v>
+      </c>
+      <c r="Q15">
+        <v>22.783</v>
+      </c>
+      <c r="R15">
+        <v>1122.952</v>
+      </c>
+      <c r="S15">
+        <v>225</v>
+      </c>
+      <c r="T15">
+        <v>217</v>
+      </c>
+      <c r="U15">
+        <v>506</v>
+      </c>
+      <c r="V15">
+        <v>23583.32181</v>
+      </c>
+      <c r="W15">
+        <v>14708.32748</v>
+      </c>
+      <c r="X15">
+        <v>57392.75647</v>
+      </c>
+      <c r="Y15">
+        <v>19367</v>
+      </c>
+      <c r="Z15">
+        <v>1040</v>
+      </c>
+      <c r="AA15">
+        <v>39863017.65126469</v>
+      </c>
+      <c r="AB15">
+        <v>1781051.42116928</v>
+      </c>
+      <c r="AC15">
+        <v>69842.8725866976</v>
+      </c>
+      <c r="AD15">
+        <v>35837.81295795665</v>
+      </c>
+      <c r="AE15">
+        <v>4670.760092033179</v>
+      </c>
+      <c r="AF15">
+        <v>10124.81774404847</v>
+      </c>
+      <c r="AG15">
+        <v>1.863686870055606</v>
+      </c>
+      <c r="AH15">
+        <v>2.920489110350345</v>
+      </c>
+      <c r="AI15">
+        <v>0.216580864634862</v>
+      </c>
+      <c r="AJ15">
+        <v>2.028848962377733</v>
+      </c>
+      <c r="AK15">
+        <v>22.38173315911013</v>
+      </c>
+      <c r="AL15">
+        <v>5.369959208963701</v>
+      </c>
+      <c r="AM15">
+        <v>0.9540640704168892</v>
+      </c>
+      <c r="AN15">
+        <v>1.475354694781381</v>
+      </c>
+      <c r="AO15">
+        <v>0.8816443591875454</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>8894.92</v>
+      </c>
+      <c r="C16">
+        <v>23131.102</v>
+      </c>
+      <c r="D16">
+        <v>2.600484546235379</v>
+      </c>
+      <c r="E16">
+        <v>0.1654200910963948</v>
+      </c>
+      <c r="F16">
+        <v>0.5899111160777134</v>
+      </c>
+      <c r="G16">
+        <v>1207421000</v>
+      </c>
+      <c r="H16">
+        <v>230182000</v>
+      </c>
+      <c r="I16">
+        <v>130463000</v>
+      </c>
+      <c r="J16">
+        <v>148249000</v>
+      </c>
+      <c r="K16">
+        <v>9.347</v>
+      </c>
+      <c r="L16">
+        <v>611.479</v>
+      </c>
+      <c r="M16">
+        <v>57.495</v>
+      </c>
+      <c r="N16">
+        <v>3410.627</v>
+      </c>
+      <c r="O16">
+        <v>5.63</v>
+      </c>
+      <c r="P16">
+        <v>174.725</v>
+      </c>
+      <c r="Q16">
+        <v>82.23</v>
+      </c>
+      <c r="R16">
+        <v>909.476</v>
+      </c>
+      <c r="S16">
+        <v>85</v>
+      </c>
+      <c r="T16">
+        <v>52</v>
+      </c>
+      <c r="U16">
+        <v>199</v>
+      </c>
+      <c r="V16">
+        <v>11477.24021</v>
+      </c>
+      <c r="W16">
+        <v>6920.14602</v>
+      </c>
+      <c r="X16">
+        <v>14314.68906</v>
+      </c>
+      <c r="Y16">
+        <v>23835</v>
+      </c>
+      <c r="Z16">
+        <v>4604</v>
+      </c>
+      <c r="AA16">
+        <v>5211877.839613175</v>
+      </c>
+      <c r="AB16">
+        <v>774814.288480103</v>
+      </c>
+      <c r="AC16">
+        <v>52199.02622884115</v>
+      </c>
+      <c r="AD16">
+        <v>9951.190392917726</v>
+      </c>
+      <c r="AE16">
+        <v>5640.154974025882</v>
+      </c>
+      <c r="AF16">
+        <v>6409.076402844967</v>
+      </c>
+      <c r="AG16">
+        <v>1.528588880403088</v>
+      </c>
+      <c r="AH16">
+        <v>3.22220632422378</v>
+      </c>
+      <c r="AI16">
+        <v>1.68576041883208</v>
+      </c>
+      <c r="AJ16">
+        <v>9.041470033293898</v>
+      </c>
+      <c r="AK16">
+        <v>6.726615547884304</v>
+      </c>
+      <c r="AL16">
+        <v>19.31613173903923</v>
+      </c>
+      <c r="AM16">
+        <v>0.7405961576541753</v>
+      </c>
+      <c r="AN16">
+        <v>0.7514292306797307</v>
+      </c>
+      <c r="AO16">
+        <v>1.390180388591689</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>10297.118</v>
+      </c>
+      <c r="C17">
+        <v>24049.301</v>
+      </c>
+      <c r="D17">
+        <v>2.335537089115615</v>
+      </c>
+      <c r="E17">
+        <v>0.1248976009739327</v>
+      </c>
+      <c r="F17">
+        <v>0.4454022646077921</v>
+      </c>
+      <c r="G17">
+        <v>1036860000</v>
+      </c>
+      <c r="H17">
+        <v>199028000</v>
+      </c>
+      <c r="I17">
+        <v>131228000</v>
+      </c>
+      <c r="J17">
+        <v>445599000</v>
+      </c>
+      <c r="K17">
+        <v>3.95</v>
+      </c>
+      <c r="L17">
+        <v>639.191</v>
+      </c>
+      <c r="M17">
+        <v>12.554</v>
+      </c>
+      <c r="N17">
+        <v>2628.275</v>
+      </c>
+      <c r="O17">
+        <v>6.52</v>
+      </c>
+      <c r="P17">
+        <v>234.029</v>
+      </c>
+      <c r="Q17">
+        <v>21.478</v>
+      </c>
+      <c r="R17">
+        <v>280.945</v>
+      </c>
+      <c r="S17">
+        <v>76</v>
+      </c>
+      <c r="T17">
+        <v>64</v>
+      </c>
+      <c r="U17">
+        <v>269</v>
+      </c>
+      <c r="V17">
+        <v>8345.15602</v>
+      </c>
+      <c r="W17">
+        <v>7081.39788</v>
+      </c>
+      <c r="X17">
+        <v>15907.0897</v>
+      </c>
+      <c r="Y17">
+        <v>24931</v>
+      </c>
+      <c r="Z17">
+        <v>1294</v>
+      </c>
+      <c r="AA17">
+        <v>4883779.465176751</v>
+      </c>
+      <c r="AB17">
+        <v>687783.6008255004</v>
+      </c>
+      <c r="AC17">
+        <v>43113.93499544956</v>
+      </c>
+      <c r="AD17">
+        <v>8275.833048120609</v>
+      </c>
+      <c r="AE17">
+        <v>5456.624290244445</v>
+      </c>
+      <c r="AF17">
+        <v>18528.56347051417</v>
+      </c>
+      <c r="AG17">
+        <v>0.617968650997902</v>
+      </c>
+      <c r="AH17">
+        <v>2.785979515359208</v>
+      </c>
+      <c r="AI17">
+        <v>0.477651691698928</v>
+      </c>
+      <c r="AJ17">
+        <v>7.644912705333786</v>
+      </c>
+      <c r="AK17">
+        <v>7.100750089584978</v>
+      </c>
+      <c r="AL17">
+        <v>5.190325297821988</v>
+      </c>
+      <c r="AM17">
+        <v>0.9107079582198153</v>
+      </c>
+      <c r="AN17">
+        <v>0.9037763600426303</v>
+      </c>
+      <c r="AO17">
+        <v>1.691069863018375</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>27706.969</v>
+      </c>
+      <c r="C18">
+        <v>62420.024</v>
+      </c>
+      <c r="D18">
+        <v>2.252863674839352</v>
+      </c>
+      <c r="E18">
+        <v>0.1468702735519615</v>
+      </c>
+      <c r="F18">
+        <v>0.5237598795613583</v>
+      </c>
+      <c r="G18">
+        <v>1516610000</v>
+      </c>
+      <c r="H18">
+        <v>520457000</v>
+      </c>
+      <c r="I18">
+        <v>39760000</v>
+      </c>
+      <c r="J18">
+        <v>534263000</v>
+      </c>
+      <c r="K18">
+        <v>8.417999999999999</v>
+      </c>
+      <c r="L18">
+        <v>709.895</v>
+      </c>
+      <c r="M18">
+        <v>3.451</v>
+      </c>
+      <c r="N18">
+        <v>1245.474</v>
+      </c>
+      <c r="O18">
+        <v>9.219000000000001</v>
+      </c>
+      <c r="P18">
+        <v>232.509</v>
+      </c>
+      <c r="Q18">
+        <v>36.02</v>
+      </c>
+      <c r="R18">
+        <v>608.885</v>
+      </c>
+      <c r="S18">
+        <v>142</v>
+      </c>
+      <c r="T18">
+        <v>116</v>
+      </c>
+      <c r="U18">
+        <v>485</v>
+      </c>
+      <c r="V18">
+        <v>13605.65361</v>
+      </c>
+      <c r="W18">
+        <v>12060.30418</v>
+      </c>
+      <c r="X18">
+        <v>22381.16617</v>
+      </c>
+      <c r="Y18">
+        <v>14482</v>
+      </c>
+      <c r="Z18">
+        <v>1013</v>
+      </c>
+      <c r="AA18">
+        <v>18799332.01260468</v>
+      </c>
+      <c r="AB18">
+        <v>1158585.130568407</v>
+      </c>
+      <c r="AC18">
+        <v>24296.85063882705</v>
+      </c>
+      <c r="AD18">
+        <v>8337.981414425602</v>
+      </c>
+      <c r="AE18">
+        <v>636.9750835084587</v>
+      </c>
+      <c r="AF18">
+        <v>8559.160438643856</v>
+      </c>
+      <c r="AG18">
+        <v>1.185809168961607</v>
+      </c>
+      <c r="AH18">
+        <v>3.96500780614944</v>
+      </c>
+      <c r="AI18">
+        <v>0.2770832630789563</v>
+      </c>
+      <c r="AJ18">
+        <v>5.915731213611767</v>
+      </c>
+      <c r="AK18">
+        <v>16.22611193307965</v>
+      </c>
+      <c r="AL18">
+        <v>6.994890208534733</v>
+      </c>
+      <c r="AM18">
+        <v>1.043683780804412</v>
+      </c>
+      <c r="AN18">
+        <v>0.9618331201991293</v>
+      </c>
+      <c r="AO18">
+        <v>2.167000576806851</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>17042.114</v>
+      </c>
+      <c r="C19">
+        <v>40044.769</v>
+      </c>
+      <c r="D19">
+        <v>2.349753616247374</v>
+      </c>
+      <c r="E19">
+        <v>0.2794516057765248</v>
+      </c>
+      <c r="F19">
+        <v>0.9965634014629779</v>
+      </c>
+      <c r="G19">
+        <v>1190251000</v>
+      </c>
+      <c r="H19">
+        <v>476902000</v>
+      </c>
+      <c r="I19">
+        <v>54472000</v>
+      </c>
+      <c r="J19">
+        <v>1575525000</v>
+      </c>
+      <c r="K19">
+        <v>23.54</v>
+      </c>
+      <c r="L19">
+        <v>527.2140000000001</v>
+      </c>
+      <c r="M19">
+        <v>28.774</v>
+      </c>
+      <c r="N19">
+        <v>1007.079</v>
+      </c>
+      <c r="O19">
+        <v>57.15600000000001</v>
+      </c>
+      <c r="P19">
+        <v>413.912</v>
+      </c>
+      <c r="Q19">
+        <v>168.381</v>
+      </c>
+      <c r="R19">
+        <v>962.245</v>
+      </c>
+      <c r="S19">
+        <v>98</v>
+      </c>
+      <c r="T19">
+        <v>242</v>
+      </c>
+      <c r="U19">
+        <v>551</v>
+      </c>
+      <c r="V19">
+        <v>10346.78931</v>
+      </c>
+      <c r="W19">
+        <v>20067.93234</v>
+      </c>
+      <c r="X19">
+        <v>26099.31433</v>
+      </c>
+      <c r="Y19">
+        <v>12733</v>
+      </c>
+      <c r="Z19">
+        <v>1571</v>
+      </c>
+      <c r="AA19">
+        <v>49272096.32954284</v>
+      </c>
+      <c r="AB19">
+        <v>1437957.545454546</v>
+      </c>
+      <c r="AC19">
+        <v>29723.0082660734</v>
+      </c>
+      <c r="AD19">
+        <v>11909.22090223569</v>
+      </c>
+      <c r="AE19">
+        <v>1360.277543366526</v>
+      </c>
+      <c r="AF19">
+        <v>39344.0901107458</v>
+      </c>
+      <c r="AG19">
+        <v>4.464980065021035</v>
+      </c>
+      <c r="AH19">
+        <v>13.80873229092174</v>
+      </c>
+      <c r="AI19">
+        <v>2.857174064795314</v>
+      </c>
+      <c r="AJ19">
+        <v>17.49876590681168</v>
+      </c>
+      <c r="AK19">
+        <v>34.26533452624825</v>
+      </c>
+      <c r="AL19">
+        <v>12.33801931987748</v>
+      </c>
+      <c r="AM19">
+        <v>0.947153721447528</v>
+      </c>
+      <c r="AN19">
+        <v>1.205904005953012</v>
+      </c>
+      <c r="AO19">
+        <v>2.111166573317407</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>8327.236999999999</v>
+      </c>
+      <c r="C20">
+        <v>17454.922</v>
+      </c>
+      <c r="D20">
+        <v>2.096124080532354</v>
+      </c>
+      <c r="E20">
+        <v>0.1352753108836579</v>
+      </c>
+      <c r="F20">
+        <v>0.4824106255305856</v>
+      </c>
+      <c r="G20">
+        <v>533693000</v>
+      </c>
+      <c r="H20">
+        <v>237940000</v>
+      </c>
+      <c r="I20">
+        <v>46289000</v>
+      </c>
+      <c r="J20">
+        <v>109277000</v>
+      </c>
+      <c r="K20">
+        <v>0.34</v>
+      </c>
+      <c r="L20">
+        <v>279.28</v>
+      </c>
+      <c r="M20">
+        <v>17.38</v>
+      </c>
+      <c r="N20">
+        <v>791.486</v>
+      </c>
+      <c r="O20">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="P20">
+        <v>87</v>
+      </c>
+      <c r="Q20">
+        <v>12.26</v>
+      </c>
+      <c r="R20">
+        <v>129.424</v>
+      </c>
+      <c r="S20">
+        <v>40</v>
+      </c>
+      <c r="T20">
+        <v>13</v>
+      </c>
+      <c r="U20">
+        <v>127</v>
+      </c>
+      <c r="V20">
+        <v>3962.61925</v>
+      </c>
+      <c r="W20">
+        <v>2040.89122</v>
+      </c>
+      <c r="X20">
+        <v>8647.579249999999</v>
+      </c>
+      <c r="Y20">
+        <v>2505</v>
+      </c>
+      <c r="Z20">
+        <v>355</v>
+      </c>
+      <c r="AA20">
+        <v>2063713.299671782</v>
+      </c>
+      <c r="AB20">
+        <v>310402.9090909091</v>
+      </c>
+      <c r="AC20">
+        <v>30575.50185557977</v>
+      </c>
+      <c r="AD20">
+        <v>13631.68509146016</v>
+      </c>
+      <c r="AE20">
+        <v>2651.916748754306</v>
+      </c>
+      <c r="AF20">
+        <v>6260.526400519006</v>
+      </c>
+      <c r="AG20">
+        <v>0.121741621311945</v>
+      </c>
+      <c r="AH20">
+        <v>0.7586206896551724</v>
+      </c>
+      <c r="AI20">
+        <v>2.19586954159644</v>
+      </c>
+      <c r="AJ20">
+        <v>9.472740759055506</v>
+      </c>
+      <c r="AK20">
+        <v>6.648498577915626</v>
+      </c>
+      <c r="AL20">
+        <v>14.17165668662675</v>
+      </c>
+      <c r="AM20">
+        <v>1.009433343867191</v>
+      </c>
+      <c r="AN20">
+        <v>0.6369766243592345</v>
+      </c>
+      <c r="AO20">
+        <v>1.468619093603565</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>5210.482</v>
+      </c>
+      <c r="C21">
+        <v>14960.72</v>
+      </c>
+      <c r="D21">
+        <v>2.871273713257238</v>
+      </c>
+      <c r="E21">
+        <v>0.5858806260661252</v>
+      </c>
+      <c r="F21">
+        <v>2.089332025633915</v>
+      </c>
+      <c r="G21">
+        <v>1239236000</v>
+      </c>
+      <c r="H21">
+        <v>499750000</v>
+      </c>
+      <c r="I21">
+        <v>136140000</v>
+      </c>
+      <c r="J21">
+        <v>1504018000</v>
+      </c>
+      <c r="K21">
+        <v>1.749</v>
+      </c>
+      <c r="L21">
+        <v>142.136</v>
+      </c>
+      <c r="M21">
+        <v>3.277</v>
+      </c>
+      <c r="N21">
+        <v>321.031</v>
+      </c>
+      <c r="O21">
+        <v>23.254</v>
+      </c>
+      <c r="P21">
+        <v>335.886</v>
+      </c>
+      <c r="Q21">
+        <v>195.164</v>
+      </c>
+      <c r="R21">
+        <v>1020.588</v>
+      </c>
+      <c r="S21">
+        <v>6</v>
+      </c>
+      <c r="T21">
+        <v>321</v>
+      </c>
+      <c r="U21">
+        <v>230</v>
+      </c>
+      <c r="V21">
+        <v>4619.30977</v>
+      </c>
+      <c r="W21">
+        <v>31209.24831</v>
+      </c>
+      <c r="X21">
+        <v>20917.27191</v>
+      </c>
+      <c r="Y21">
+        <v>5456</v>
+      </c>
+      <c r="Z21">
+        <v>251</v>
+      </c>
+      <c r="AA21">
+        <v>136966406.6232978</v>
+      </c>
+      <c r="AB21">
+        <v>2217468.367032058</v>
+      </c>
+      <c r="AC21">
+        <v>82832.64441818309</v>
+      </c>
+      <c r="AD21">
+        <v>33404.14097717222</v>
+      </c>
+      <c r="AE21">
+        <v>9099.82941997444</v>
+      </c>
+      <c r="AF21">
+        <v>100531.1241704945</v>
+      </c>
+      <c r="AG21">
+        <v>1.230511622671244</v>
+      </c>
+      <c r="AH21">
+        <v>6.923182270174999</v>
+      </c>
+      <c r="AI21">
+        <v>1.02077369475222</v>
+      </c>
+      <c r="AJ21">
+        <v>19.12270181503212</v>
+      </c>
+      <c r="AK21">
+        <v>61.76701713522916</v>
+      </c>
+      <c r="AL21">
+        <v>4.600439882697947</v>
+      </c>
+      <c r="AM21">
+        <v>0.1298895354229513</v>
+      </c>
+      <c r="AN21">
+        <v>1.028541273444083</v>
+      </c>
+      <c r="AO21">
+        <v>1.099569776544536</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>2908.835</v>
+      </c>
+      <c r="C22">
+        <v>9279.084000000001</v>
+      </c>
+      <c r="D22">
+        <v>3.189965742298893</v>
+      </c>
+      <c r="E22">
+        <v>0.86163558816797</v>
+      </c>
+      <c r="F22">
+        <v>3.072712680180127</v>
+      </c>
+      <c r="G22">
+        <v>974656000</v>
+      </c>
+      <c r="H22">
+        <v>940648000</v>
+      </c>
+      <c r="I22">
+        <v>340527000</v>
+      </c>
+      <c r="J22">
+        <v>1518022000</v>
+      </c>
+      <c r="K22">
+        <v>2.272</v>
+      </c>
+      <c r="L22">
+        <v>62.608</v>
+      </c>
+      <c r="M22">
+        <v>1.5</v>
+      </c>
+      <c r="N22">
+        <v>104.577</v>
+      </c>
+      <c r="O22">
+        <v>18.225</v>
+      </c>
+      <c r="P22">
+        <v>503.678</v>
+      </c>
+      <c r="Q22">
+        <v>441.125</v>
+      </c>
+      <c r="R22">
+        <v>1916.739</v>
+      </c>
+      <c r="S22">
+        <v>13</v>
+      </c>
+      <c r="T22">
+        <v>220</v>
+      </c>
+      <c r="U22">
+        <v>197</v>
+      </c>
+      <c r="V22">
+        <v>1096.39109</v>
+      </c>
+      <c r="W22">
+        <v>31632.18282</v>
+      </c>
+      <c r="X22">
+        <v>24220.39017</v>
+      </c>
+      <c r="Y22">
+        <v>5252</v>
+      </c>
+      <c r="Z22">
+        <v>444</v>
+      </c>
+      <c r="AA22">
+        <v>225909410.8691963</v>
+      </c>
+      <c r="AB22">
+        <v>2385288.024276477</v>
+      </c>
+      <c r="AC22">
+        <v>105037.9541773735</v>
+      </c>
+      <c r="AD22">
+        <v>101372.9372425123</v>
+      </c>
+      <c r="AE22">
+        <v>36698.34220705405</v>
+      </c>
+      <c r="AF22">
+        <v>163596.1049603603</v>
+      </c>
+      <c r="AG22">
+        <v>3.628929210324559</v>
+      </c>
+      <c r="AH22">
+        <v>3.618383173376642</v>
+      </c>
+      <c r="AI22">
+        <v>1.434349809231475</v>
+      </c>
+      <c r="AJ22">
+        <v>23.01434884979123</v>
+      </c>
+      <c r="AK22">
+        <v>94.70948940756151</v>
+      </c>
+      <c r="AL22">
+        <v>8.453922315308454</v>
+      </c>
+      <c r="AM22">
+        <v>1.185708285900061</v>
+      </c>
+      <c r="AN22">
+        <v>0.6954942099692885</v>
+      </c>
+      <c r="AO22">
+        <v>0.8133642712494751</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Michigan</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>9663.530000000001</v>
+      </c>
+      <c r="C23">
+        <v>27385.521</v>
+      </c>
+      <c r="D23">
+        <v>2.833904484179177</v>
+      </c>
+      <c r="E23">
+        <v>0.4131138129524722</v>
+      </c>
+      <c r="F23">
+        <v>1.473221474191437</v>
+      </c>
+      <c r="G23">
+        <v>1983891000</v>
+      </c>
+      <c r="H23">
+        <v>485842000</v>
+      </c>
+      <c r="I23">
+        <v>144569000</v>
+      </c>
+      <c r="J23">
+        <v>605637000</v>
+      </c>
+      <c r="K23">
+        <v>16.06</v>
+      </c>
+      <c r="L23">
+        <v>558.1</v>
+      </c>
+      <c r="M23">
+        <v>10.853</v>
+      </c>
+      <c r="N23">
+        <v>2129.682</v>
+      </c>
+      <c r="O23">
+        <v>41.587</v>
+      </c>
+      <c r="P23">
+        <v>674.529</v>
+      </c>
+      <c r="Q23">
+        <v>210.874</v>
+      </c>
+      <c r="R23">
+        <v>1934.896</v>
+      </c>
+      <c r="S23">
+        <v>76</v>
+      </c>
+      <c r="T23">
+        <v>380</v>
+      </c>
+      <c r="U23">
+        <v>656</v>
+      </c>
+      <c r="V23">
+        <v>12495.56342</v>
+      </c>
+      <c r="W23">
+        <v>38016.06939</v>
+      </c>
+      <c r="X23">
+        <v>45389.16105</v>
+      </c>
+      <c r="Y23">
+        <v>11314</v>
+      </c>
+      <c r="Z23">
+        <v>1269</v>
+      </c>
+      <c r="AA23">
+        <v>51053538.28743049</v>
+      </c>
+      <c r="AB23">
+        <v>3038795.409069619</v>
+      </c>
+      <c r="AC23">
+        <v>72443.06215682367</v>
+      </c>
+      <c r="AD23">
+        <v>17740.83465492586</v>
+      </c>
+      <c r="AE23">
+        <v>5279.030477455587</v>
+      </c>
+      <c r="AF23">
+        <v>22115.22650965815</v>
+      </c>
+      <c r="AG23">
+        <v>2.877620498118617</v>
+      </c>
+      <c r="AH23">
+        <v>6.165339073635084</v>
+      </c>
+      <c r="AI23">
+        <v>0.5096065985438202</v>
+      </c>
+      <c r="AJ23">
+        <v>10.89846689434471</v>
+      </c>
+      <c r="AK23">
+        <v>16.80058424961931</v>
+      </c>
+      <c r="AL23">
+        <v>11.21619232808909</v>
+      </c>
+      <c r="AM23">
+        <v>0.6082158718698257</v>
+      </c>
+      <c r="AN23">
+        <v>0.9995773000665811</v>
+      </c>
+      <c r="AO23">
+        <v>1.445278971508992</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Minnesota</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>11717.215</v>
+      </c>
+      <c r="C24">
+        <v>29238.678</v>
+      </c>
+      <c r="D24">
+        <v>2.495360714982187</v>
+      </c>
+      <c r="E24">
+        <v>0.2003110400545469</v>
+      </c>
+      <c r="F24">
+        <v>0.7143371063216676</v>
+      </c>
+      <c r="G24">
+        <v>1212303000</v>
+      </c>
+      <c r="H24">
+        <v>541073000</v>
+      </c>
+      <c r="I24">
+        <v>226105000</v>
+      </c>
+      <c r="J24">
+        <v>417174000</v>
+      </c>
+      <c r="K24">
+        <v>2.196</v>
+      </c>
+      <c r="L24">
+        <v>588.081</v>
+      </c>
+      <c r="M24">
+        <v>17.819</v>
+      </c>
+      <c r="N24">
+        <v>3457.792</v>
+      </c>
+      <c r="O24">
+        <v>5.387</v>
+      </c>
+      <c r="P24">
+        <v>324.225</v>
+      </c>
+      <c r="Q24">
+        <v>8.567</v>
+      </c>
+      <c r="R24">
+        <v>623.985</v>
+      </c>
+      <c r="S24">
+        <v>65</v>
+      </c>
+      <c r="T24">
+        <v>83</v>
+      </c>
+      <c r="U24">
+        <v>293</v>
+      </c>
+      <c r="V24">
+        <v>10814.34901</v>
+      </c>
+      <c r="W24">
+        <v>17093.12797</v>
+      </c>
+      <c r="X24">
+        <v>29563.14677</v>
+      </c>
+      <c r="Y24">
+        <v>13497</v>
+      </c>
+      <c r="Z24">
+        <v>602</v>
+      </c>
+      <c r="AA24">
+        <v>38498758.85831395</v>
+      </c>
+      <c r="AB24">
+        <v>1712636.565101314</v>
+      </c>
+      <c r="AC24">
+        <v>41462.30551189763</v>
+      </c>
+      <c r="AD24">
+        <v>18505.38522979732</v>
+      </c>
+      <c r="AE24">
+        <v>7733.078766420287</v>
+      </c>
+      <c r="AF24">
+        <v>14267.88174212254</v>
+      </c>
+      <c r="AG24">
+        <v>0.3734179475276365</v>
+      </c>
+      <c r="AH24">
+        <v>1.661500501195157</v>
+      </c>
+      <c r="AI24">
+        <v>0.515328857259199</v>
+      </c>
+      <c r="AJ24">
+        <v>1.37294967026451</v>
+      </c>
+      <c r="AK24">
+        <v>22.47923444051685</v>
+      </c>
+      <c r="AL24">
+        <v>4.460250426020597</v>
+      </c>
+      <c r="AM24">
+        <v>0.601053285222205</v>
+      </c>
+      <c r="AN24">
+        <v>0.4855752565924304</v>
+      </c>
+      <c r="AO24">
+        <v>0.9910988240850248</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Mississippi</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>10948.342</v>
+      </c>
+      <c r="C25">
+        <v>28326.481</v>
+      </c>
+      <c r="D25">
+        <v>2.587284997125592</v>
+      </c>
+      <c r="E25">
+        <v>0.1715969237407216</v>
+      </c>
+      <c r="F25">
+        <v>0.6119385627735126</v>
+      </c>
+      <c r="G25">
+        <v>696862000</v>
+      </c>
+      <c r="H25">
+        <v>122836000</v>
+      </c>
+      <c r="I25">
+        <v>63319000</v>
+      </c>
+      <c r="J25">
+        <v>143118000</v>
+      </c>
+      <c r="K25">
+        <v>10.012</v>
+      </c>
+      <c r="L25">
+        <v>578.442</v>
+      </c>
+      <c r="M25">
+        <v>27.261</v>
+      </c>
+      <c r="N25">
+        <v>1783.619</v>
+      </c>
+      <c r="O25">
+        <v>11.379</v>
+      </c>
+      <c r="P25">
+        <v>253.415</v>
+      </c>
+      <c r="Q25">
+        <v>101.514</v>
+      </c>
+      <c r="R25">
+        <v>945.15</v>
+      </c>
+      <c r="S25">
+        <v>169</v>
+      </c>
+      <c r="T25">
+        <v>129</v>
+      </c>
+      <c r="U25">
+        <v>314</v>
+      </c>
+      <c r="V25">
+        <v>10156.92025</v>
+      </c>
+      <c r="W25">
+        <v>9574.75561</v>
+      </c>
+      <c r="X25">
+        <v>20220.04363</v>
+      </c>
+      <c r="Y25">
+        <v>16782</v>
+      </c>
+      <c r="Z25">
+        <v>1097</v>
+      </c>
+      <c r="AA25">
+        <v>3877774.478981165</v>
+      </c>
+      <c r="AB25">
+        <v>531233.8242078114</v>
+      </c>
+      <c r="AC25">
+        <v>24601.07911039144</v>
+      </c>
+      <c r="AD25">
+        <v>4336.436989825881</v>
+      </c>
+      <c r="AE25">
+        <v>2235.328843000301</v>
+      </c>
+      <c r="AF25">
+        <v>5052.445448483347</v>
+      </c>
+      <c r="AG25">
+        <v>1.730856334775138</v>
+      </c>
+      <c r="AH25">
+        <v>4.490263007320008</v>
+      </c>
+      <c r="AI25">
+        <v>1.528409374423574</v>
+      </c>
+      <c r="AJ25">
+        <v>10.74051737819394</v>
+      </c>
+      <c r="AK25">
+        <v>7.299562456821712</v>
+      </c>
+      <c r="AL25">
+        <v>6.536765582171373</v>
+      </c>
+      <c r="AM25">
+        <v>1.663890193486554</v>
+      </c>
+      <c r="AN25">
+        <v>1.347292873619361</v>
+      </c>
+      <c r="AO25">
+        <v>1.55291455224224</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>33808.504</v>
+      </c>
+      <c r="C26">
+        <v>77641.64999999998</v>
+      </c>
+      <c r="D26">
+        <v>2.296512439592121</v>
+      </c>
+      <c r="E26">
+        <v>0.1438985647522947</v>
+      </c>
+      <c r="F26">
+        <v>0.5131623515159419</v>
+      </c>
+      <c r="G26">
+        <v>1096090000</v>
+      </c>
+      <c r="H26">
+        <v>554241000</v>
+      </c>
+      <c r="I26">
+        <v>80754000</v>
+      </c>
+      <c r="J26">
+        <v>566331000</v>
+      </c>
+      <c r="K26">
+        <v>7.074</v>
+      </c>
+      <c r="L26">
+        <v>846.777</v>
+      </c>
+      <c r="M26">
+        <v>9.147</v>
+      </c>
+      <c r="N26">
+        <v>1884.928</v>
+      </c>
+      <c r="O26">
+        <v>17.078</v>
+      </c>
+      <c r="P26">
+        <v>538.211</v>
+      </c>
+      <c r="Q26">
+        <v>71.04300000000001</v>
+      </c>
+      <c r="R26">
+        <v>870.6789999999999</v>
+      </c>
+      <c r="S26">
+        <v>206</v>
+      </c>
+      <c r="T26">
+        <v>272</v>
+      </c>
+      <c r="U26">
+        <v>513</v>
+      </c>
+      <c r="V26">
+        <v>16983.08332</v>
+      </c>
+      <c r="W26">
+        <v>25222.24245</v>
+      </c>
+      <c r="X26">
+        <v>37225.51936000001</v>
+      </c>
+      <c r="Y26">
+        <v>24569</v>
+      </c>
+      <c r="Z26">
+        <v>2230</v>
+      </c>
+      <c r="AA26">
+        <v>29460393.53881588</v>
+      </c>
+      <c r="AB26">
+        <v>1943927.065610533</v>
+      </c>
+      <c r="AC26">
+        <v>14117.29400392702</v>
+      </c>
+      <c r="AD26">
+        <v>7138.449530632079</v>
+      </c>
+      <c r="AE26">
+        <v>1040.086087814981</v>
+      </c>
+      <c r="AF26">
+        <v>7294.164923079303</v>
+      </c>
+      <c r="AG26">
+        <v>0.8354029455216662</v>
+      </c>
+      <c r="AH26">
+        <v>3.173104971841898</v>
+      </c>
+      <c r="AI26">
+        <v>0.4852705249219068</v>
+      </c>
+      <c r="AJ26">
+        <v>8.159493912222532</v>
+      </c>
+      <c r="AK26">
+        <v>15.15509200936157</v>
+      </c>
+      <c r="AL26">
+        <v>9.076478489152997</v>
+      </c>
+      <c r="AM26">
+        <v>1.212971732626464</v>
+      </c>
+      <c r="AN26">
+        <v>1.07841323204789</v>
+      </c>
+      <c r="AO26">
+        <v>1.37808688453447</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>11041.242</v>
+      </c>
+      <c r="C27">
+        <v>25244.595</v>
+      </c>
+      <c r="D27">
+        <v>2.286390878852216</v>
+      </c>
+      <c r="E27">
+        <v>0.06134382429189297</v>
+      </c>
+      <c r="F27">
+        <v>0.2187606330806476</v>
+      </c>
+      <c r="G27">
+        <v>455575000</v>
+      </c>
+      <c r="H27">
+        <v>142759000</v>
+      </c>
+      <c r="I27">
+        <v>56528000</v>
+      </c>
+      <c r="J27">
+        <v>76709000</v>
+      </c>
+      <c r="K27">
+        <v>5.7</v>
+      </c>
+      <c r="L27">
+        <v>1095.071</v>
+      </c>
+      <c r="M27">
+        <v>21.09</v>
+      </c>
+      <c r="N27">
+        <v>2771.57</v>
+      </c>
+      <c r="O27">
+        <v>0.3</v>
+      </c>
+      <c r="P27">
+        <v>97.688</v>
+      </c>
+      <c r="Q27">
+        <v>24.018</v>
+      </c>
+      <c r="R27">
+        <v>257.648</v>
+      </c>
+      <c r="S27">
+        <v>93</v>
+      </c>
+      <c r="T27">
+        <v>28</v>
+      </c>
+      <c r="U27">
+        <v>90</v>
+      </c>
+      <c r="V27">
+        <v>5499.07317</v>
+      </c>
+      <c r="W27">
+        <v>1943.85531</v>
+      </c>
+      <c r="X27">
+        <v>6070.85163</v>
+      </c>
+      <c r="Y27">
+        <v>5278</v>
+      </c>
+      <c r="Z27">
+        <v>367</v>
+      </c>
+      <c r="AA27">
+        <v>2191568.057901517</v>
+      </c>
+      <c r="AB27">
+        <v>160577.9090909091</v>
+      </c>
+      <c r="AC27">
+        <v>18046.43726706647</v>
+      </c>
+      <c r="AD27">
+        <v>5655.032295031867</v>
+      </c>
+      <c r="AE27">
+        <v>2239.21199765732</v>
+      </c>
+      <c r="AF27">
+        <v>3038.630645490648</v>
+      </c>
+      <c r="AG27">
+        <v>0.5205141949700066</v>
+      </c>
+      <c r="AH27">
+        <v>0.3071001555974122</v>
+      </c>
+      <c r="AI27">
+        <v>0.7609405499410081</v>
+      </c>
+      <c r="AJ27">
+        <v>9.322020741476743</v>
+      </c>
+      <c r="AK27">
+        <v>13.64800469945582</v>
+      </c>
+      <c r="AL27">
+        <v>6.953391436150056</v>
+      </c>
+      <c r="AM27">
+        <v>1.691194081711046</v>
+      </c>
+      <c r="AN27">
+        <v>1.440436428367706</v>
+      </c>
+      <c r="AO27">
+        <v>1.482493816110607</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>9937.090000000002</v>
+      </c>
+      <c r="C28">
+        <v>22595.78</v>
+      </c>
+      <c r="D28">
+        <v>2.27388299794004</v>
+      </c>
+      <c r="E28">
+        <v>0.08304205475535698</v>
+      </c>
+      <c r="F28">
+        <v>0.2961395491770882</v>
+      </c>
+      <c r="G28">
+        <v>668685000</v>
+      </c>
+      <c r="H28">
+        <v>152980000</v>
+      </c>
+      <c r="I28">
+        <v>80319000</v>
+      </c>
+      <c r="J28">
+        <v>71356000</v>
+      </c>
+      <c r="K28">
+        <v>2.99</v>
+      </c>
+      <c r="L28">
+        <v>414.49</v>
+      </c>
+      <c r="M28">
+        <v>33.7</v>
+      </c>
+      <c r="N28">
+        <v>2290.11</v>
+      </c>
+      <c r="O28">
+        <v>2.28</v>
+      </c>
+      <c r="P28">
+        <v>68.83</v>
+      </c>
+      <c r="Q28">
+        <v>91.70999999999999</v>
+      </c>
+      <c r="R28">
+        <v>304.17</v>
+      </c>
+      <c r="S28">
+        <v>71</v>
+      </c>
+      <c r="T28">
+        <v>52</v>
+      </c>
+      <c r="U28">
+        <v>121</v>
+      </c>
+      <c r="V28">
+        <v>6339.70196</v>
+      </c>
+      <c r="W28">
+        <v>4964.85203</v>
+      </c>
+      <c r="X28">
+        <v>9965.7749</v>
+      </c>
+      <c r="Y28">
+        <v>15336</v>
+      </c>
+      <c r="Z28">
+        <v>1220</v>
+      </c>
+      <c r="AA28">
+        <v>6489454.36880176</v>
+      </c>
+      <c r="AB28">
+        <v>555752.852356503</v>
+      </c>
+      <c r="AC28">
+        <v>29593.3576977648</v>
+      </c>
+      <c r="AD28">
+        <v>6770.290735703747</v>
+      </c>
+      <c r="AE28">
+        <v>3554.601788475547</v>
+      </c>
+      <c r="AF28">
+        <v>3157.934800214908</v>
+      </c>
+      <c r="AG28">
+        <v>0.7213684286713792</v>
+      </c>
+      <c r="AH28">
+        <v>3.312509080342875</v>
+      </c>
+      <c r="AI28">
+        <v>1.471545034954653</v>
+      </c>
+      <c r="AJ28">
+        <v>30.15090245586349</v>
+      </c>
+      <c r="AK28">
+        <v>11.67687100711256</v>
+      </c>
+      <c r="AL28">
+        <v>7.955138236828378</v>
+      </c>
+      <c r="AM28">
+        <v>1.11992646417719</v>
+      </c>
+      <c r="AN28">
+        <v>1.047362533380476</v>
+      </c>
+      <c r="AO28">
+        <v>1.214155459200669</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>5355.837</v>
+      </c>
+      <c r="C29">
+        <v>13531.282</v>
+      </c>
+      <c r="D29">
+        <v>2.52645515537534</v>
+      </c>
+      <c r="E29">
+        <v>0.2040489585539641</v>
+      </c>
+      <c r="F29">
+        <v>0.7276670450200676</v>
+      </c>
+      <c r="G29">
+        <v>649197000</v>
+      </c>
+      <c r="H29">
+        <v>169034000</v>
+      </c>
+      <c r="I29">
+        <v>229241000</v>
+      </c>
+      <c r="J29">
+        <v>193138000</v>
+      </c>
+      <c r="K29">
+        <v>1.249</v>
+      </c>
+      <c r="L29">
+        <v>456.674</v>
+      </c>
+      <c r="M29">
+        <v>1.427</v>
+      </c>
+      <c r="N29">
+        <v>1520.372</v>
+      </c>
+      <c r="O29">
+        <v>4.438999999999999</v>
+      </c>
+      <c r="P29">
+        <v>161.597</v>
+      </c>
+      <c r="Q29">
+        <v>18.232</v>
+      </c>
+      <c r="R29">
+        <v>378.261</v>
+      </c>
+      <c r="S29">
+        <v>86</v>
+      </c>
+      <c r="T29">
+        <v>98</v>
+      </c>
+      <c r="U29">
+        <v>232</v>
+      </c>
+      <c r="V29">
+        <v>4380.37523</v>
+      </c>
+      <c r="W29">
+        <v>9745.32998</v>
+      </c>
+      <c r="X29">
+        <v>13521.65165</v>
+      </c>
+      <c r="Y29">
+        <v>2071</v>
+      </c>
+      <c r="Z29">
+        <v>29</v>
+      </c>
+      <c r="AA29">
+        <v>37330527.72727272</v>
+      </c>
+      <c r="AB29">
+        <v>1035106.363636364</v>
+      </c>
+      <c r="AC29">
+        <v>47977.49392851321</v>
+      </c>
+      <c r="AD29">
+        <v>12492.09054988286</v>
+      </c>
+      <c r="AE29">
+        <v>16941.55808740074</v>
+      </c>
+      <c r="AF29">
+        <v>14273.44430483379</v>
+      </c>
+      <c r="AG29">
+        <v>0.2734992576761542</v>
+      </c>
+      <c r="AH29">
+        <v>2.746956936081734</v>
+      </c>
+      <c r="AI29">
+        <v>0.09385860828797163</v>
+      </c>
+      <c r="AJ29">
+        <v>4.819952360935967</v>
+      </c>
+      <c r="AK29">
+        <v>36.06443650498806</v>
+      </c>
+      <c r="AL29">
+        <v>1.400289715113472</v>
+      </c>
+      <c r="AM29">
+        <v>1.963302125603518</v>
+      </c>
+      <c r="AN29">
+        <v>1.005609868533154</v>
+      </c>
+      <c r="AO29">
+        <v>1.71576672735834</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>3890.541</v>
+      </c>
+      <c r="C30">
+        <v>8453.594999999998</v>
+      </c>
+      <c r="D30">
+        <v>2.172858479064993</v>
+      </c>
+      <c r="E30">
+        <v>0.2088264223682351</v>
+      </c>
+      <c r="F30">
+        <v>0.7447041472971739</v>
+      </c>
+      <c r="G30">
+        <v>204976000</v>
+      </c>
+      <c r="H30">
+        <v>114273000</v>
+      </c>
+      <c r="I30">
+        <v>131905000</v>
+      </c>
+      <c r="J30">
+        <v>186690000</v>
+      </c>
+      <c r="K30">
+        <v>0.1</v>
+      </c>
+      <c r="L30">
+        <v>141.961</v>
+      </c>
+      <c r="M30">
+        <v>2.077</v>
+      </c>
+      <c r="N30">
+        <v>322.743</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>83.04600000000001</v>
+      </c>
+      <c r="Q30">
+        <v>9.805999999999999</v>
+      </c>
+      <c r="R30">
+        <v>223.435</v>
+      </c>
+      <c r="S30">
+        <v>25</v>
+      </c>
+      <c r="T30">
+        <v>29</v>
+      </c>
+      <c r="U30">
+        <v>92</v>
+      </c>
+      <c r="V30">
+        <v>2344.49357</v>
+      </c>
+      <c r="W30">
+        <v>4571.304120000001</v>
+      </c>
+      <c r="X30">
+        <v>6364.765729999999</v>
+      </c>
+      <c r="Y30">
+        <v>2531</v>
+      </c>
+      <c r="Z30">
+        <v>190</v>
+      </c>
+      <c r="AA30">
+        <v>7005373.627815953</v>
+      </c>
+      <c r="AB30">
+        <v>212834.521645845</v>
+      </c>
+      <c r="AC30">
+        <v>24247.19897274474</v>
+      </c>
+      <c r="AD30">
+        <v>13517.6809392927</v>
+      </c>
+      <c r="AE30">
+        <v>15603.42079316552</v>
+      </c>
+      <c r="AF30">
+        <v>22084.09558300345</v>
+      </c>
+      <c r="AG30">
+        <v>0.07044188192531751</v>
+      </c>
+      <c r="AH30">
+        <v>0</v>
+      </c>
+      <c r="AI30">
+        <v>0.6435461032462362</v>
+      </c>
+      <c r="AJ30">
+        <v>4.388748405576566</v>
+      </c>
+      <c r="AK30">
+        <v>32.91464924789241</v>
+      </c>
+      <c r="AL30">
+        <v>7.506914263137101</v>
+      </c>
+      <c r="AM30">
+        <v>1.066328367025549</v>
+      </c>
+      <c r="AN30">
+        <v>0.634392270536575</v>
+      </c>
+      <c r="AO30">
+        <v>1.445457757641616</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>2330.18</v>
+      </c>
+      <c r="C31">
+        <v>8561.545</v>
+      </c>
+      <c r="D31">
+        <v>3.674198988919311</v>
+      </c>
+      <c r="E31">
+        <v>0.8906474240338631</v>
+      </c>
+      <c r="F31">
+        <v>3.17617293317406</v>
+      </c>
+      <c r="G31">
+        <v>1912849000</v>
+      </c>
+      <c r="H31">
+        <v>413972000</v>
+      </c>
+      <c r="I31">
+        <v>81466000</v>
+      </c>
+      <c r="J31">
+        <v>3235555000</v>
+      </c>
+      <c r="K31">
+        <v>0.23</v>
+      </c>
+      <c r="L31">
+        <v>44.88</v>
+      </c>
+      <c r="M31">
+        <v>1.7</v>
+      </c>
+      <c r="N31">
+        <v>159.64</v>
+      </c>
+      <c r="O31">
+        <v>25.37</v>
+      </c>
+      <c r="P31">
+        <v>386.66</v>
+      </c>
+      <c r="Q31">
+        <v>276.23</v>
+      </c>
+      <c r="R31">
+        <v>1798.85</v>
+      </c>
+      <c r="S31">
+        <v>17</v>
+      </c>
+      <c r="T31">
+        <v>358</v>
+      </c>
+      <c r="U31">
+        <v>304</v>
+      </c>
+      <c r="V31">
+        <v>2319.91306</v>
+      </c>
+      <c r="W31">
+        <v>43378.61639</v>
+      </c>
+      <c r="X31">
+        <v>29589.04104</v>
+      </c>
+      <c r="Y31">
+        <v>6805</v>
+      </c>
+      <c r="Z31">
+        <v>455</v>
+      </c>
+      <c r="AA31">
+        <v>306487327.3736885</v>
+      </c>
+      <c r="AB31">
+        <v>2949178.568316643</v>
+      </c>
+      <c r="AC31">
+        <v>223423.3423990647</v>
+      </c>
+      <c r="AD31">
+        <v>48352.48778111894</v>
+      </c>
+      <c r="AE31">
+        <v>9515.338645069318</v>
+      </c>
+      <c r="AF31">
+        <v>377917.186676003</v>
+      </c>
+      <c r="AG31">
+        <v>0.5124777183600713</v>
+      </c>
+      <c r="AH31">
+        <v>6.561320022759013</v>
+      </c>
+      <c r="AI31">
+        <v>1.064896016036081</v>
+      </c>
+      <c r="AJ31">
+        <v>15.35592183895267</v>
+      </c>
+      <c r="AK31">
+        <v>103.9229467711167</v>
+      </c>
+      <c r="AL31">
+        <v>6.686260102865541</v>
+      </c>
+      <c r="AM31">
+        <v>0.7327860812163366</v>
+      </c>
+      <c r="AN31">
+        <v>0.8252914218871423</v>
+      </c>
+      <c r="AO31">
+        <v>1.027407409348066</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>11913.904</v>
+      </c>
+      <c r="C32">
+        <v>29442.371</v>
+      </c>
+      <c r="D32">
+        <v>2.47126139341059</v>
+      </c>
+      <c r="E32">
+        <v>0.113845790476589</v>
+      </c>
+      <c r="F32">
+        <v>0.4059899669723842</v>
+      </c>
+      <c r="G32">
+        <v>607404000</v>
+      </c>
+      <c r="H32">
+        <v>97384000</v>
+      </c>
+      <c r="I32">
+        <v>287587000</v>
+      </c>
+      <c r="J32">
+        <v>237356000</v>
+      </c>
+      <c r="K32">
+        <v>27.96</v>
+      </c>
+      <c r="L32">
+        <v>843.9919999999998</v>
+      </c>
+      <c r="M32">
+        <v>27.942</v>
+      </c>
+      <c r="N32">
+        <v>1915.738</v>
+      </c>
+      <c r="O32">
+        <v>7.273999999999999</v>
+      </c>
+      <c r="P32">
+        <v>155.402</v>
+      </c>
+      <c r="Q32">
+        <v>98.422</v>
+      </c>
+      <c r="R32">
+        <v>702.441</v>
+      </c>
+      <c r="S32">
+        <v>147</v>
+      </c>
+      <c r="T32">
+        <v>130</v>
+      </c>
+      <c r="U32">
+        <v>189</v>
+      </c>
+      <c r="V32">
+        <v>8474.12103</v>
+      </c>
+      <c r="W32">
+        <v>6926.16498</v>
+      </c>
+      <c r="X32">
+        <v>11431.16229</v>
+      </c>
+      <c r="Y32">
+        <v>4033</v>
+      </c>
+      <c r="Z32">
+        <v>199</v>
+      </c>
+      <c r="AA32">
+        <v>8670789.293711048</v>
+      </c>
+      <c r="AB32">
+        <v>516223.1458548249</v>
+      </c>
+      <c r="AC32">
+        <v>20630.26785444691</v>
+      </c>
+      <c r="AD32">
+        <v>3307.61405051244</v>
+      </c>
+      <c r="AE32">
+        <v>9767.793497337561</v>
+      </c>
+      <c r="AF32">
+        <v>8061.714866645761</v>
+      </c>
+      <c r="AG32">
+        <v>3.312827609740377</v>
+      </c>
+      <c r="AH32">
+        <v>4.680763439337975</v>
+      </c>
+      <c r="AI32">
+        <v>1.458550177529495</v>
+      </c>
+      <c r="AJ32">
+        <v>14.01142587064252</v>
+      </c>
+      <c r="AK32">
+        <v>16.79659148051741</v>
+      </c>
+      <c r="AL32">
+        <v>4.934292090255394</v>
+      </c>
+      <c r="AM32">
+        <v>1.734693185046473</v>
+      </c>
+      <c r="AN32">
+        <v>1.876940563434283</v>
+      </c>
+      <c r="AO32">
+        <v>1.653375179226853</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>15055.825</v>
+      </c>
+      <c r="C33">
+        <v>38044.092</v>
+      </c>
+      <c r="D33">
+        <v>2.526868637221806</v>
+      </c>
+      <c r="E33">
+        <v>0.4430327053146649</v>
+      </c>
+      <c r="F33">
+        <v>1.579916417158826</v>
+      </c>
+      <c r="G33">
+        <v>3596634000</v>
+      </c>
+      <c r="H33">
+        <v>1473304000</v>
+      </c>
+      <c r="I33">
+        <v>604968000</v>
+      </c>
+      <c r="J33">
+        <v>2042747000</v>
+      </c>
+      <c r="K33">
+        <v>27.183</v>
+      </c>
+      <c r="L33">
+        <v>797.33</v>
+      </c>
+      <c r="M33">
+        <v>21.757</v>
+      </c>
+      <c r="N33">
+        <v>2070.53</v>
+      </c>
+      <c r="O33">
+        <v>88.46599999999999</v>
+      </c>
+      <c r="P33">
+        <v>916.357</v>
+      </c>
+      <c r="Q33">
+        <v>727.3619999999999</v>
+      </c>
+      <c r="R33">
+        <v>3055.688</v>
+      </c>
+      <c r="S33">
+        <v>69</v>
+      </c>
+      <c r="T33">
+        <v>468</v>
+      </c>
+      <c r="U33">
+        <v>636</v>
+      </c>
+      <c r="V33">
+        <v>10237.43013</v>
+      </c>
+      <c r="W33">
+        <v>54135.58476</v>
+      </c>
+      <c r="X33">
+        <v>51009.29979</v>
+      </c>
+      <c r="Y33">
+        <v>17557</v>
+      </c>
+      <c r="Z33">
+        <v>1611</v>
+      </c>
+      <c r="AA33">
+        <v>309049490.3718554</v>
+      </c>
+      <c r="AB33">
+        <v>4550321.489443725</v>
+      </c>
+      <c r="AC33">
+        <v>94538.56856407561</v>
+      </c>
+      <c r="AD33">
+        <v>38726.22324643732</v>
+      </c>
+      <c r="AE33">
+        <v>15901.75946372961</v>
+      </c>
+      <c r="AF33">
+        <v>53694.19777451911</v>
+      </c>
+      <c r="AG33">
+        <v>3.409253383166318</v>
+      </c>
+      <c r="AH33">
+        <v>9.654097693366232</v>
+      </c>
+      <c r="AI33">
+        <v>1.050793758119902</v>
+      </c>
+      <c r="AJ33">
+        <v>23.80354277007338</v>
+      </c>
+      <c r="AK33">
+        <v>67.91816602163567</v>
+      </c>
+      <c r="AL33">
+        <v>9.175827305348294</v>
+      </c>
+      <c r="AM33">
+        <v>0.6739972739623474</v>
+      </c>
+      <c r="AN33">
+        <v>0.8644960649724032</v>
+      </c>
+      <c r="AO33">
+        <v>1.246831465278579</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>North Carolina</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>80384.47899999999</v>
+      </c>
+      <c r="C34">
+        <v>174087.794</v>
+      </c>
+      <c r="D34">
+        <v>2.165689150016137</v>
+      </c>
+      <c r="E34">
+        <v>0.2891424484361035</v>
+      </c>
+      <c r="F34">
+        <v>1.031122297974009</v>
+      </c>
+      <c r="G34">
+        <v>4403076000</v>
+      </c>
+      <c r="H34">
+        <v>1084107000</v>
+      </c>
+      <c r="I34">
+        <v>123873000</v>
+      </c>
+      <c r="J34">
+        <v>587919000</v>
+      </c>
+      <c r="K34">
+        <v>5.464</v>
+      </c>
+      <c r="L34">
+        <v>595.252</v>
+      </c>
+      <c r="M34">
+        <v>8.019999999999998</v>
+      </c>
+      <c r="N34">
+        <v>1615.925</v>
+      </c>
+      <c r="O34">
+        <v>17.606</v>
+      </c>
+      <c r="P34">
+        <v>799.349</v>
+      </c>
+      <c r="Q34">
+        <v>95.96899999999999</v>
+      </c>
+      <c r="R34">
+        <v>1996.409</v>
+      </c>
+      <c r="S34">
+        <v>260</v>
+      </c>
+      <c r="T34">
+        <v>301</v>
+      </c>
+      <c r="U34">
+        <v>1068</v>
+      </c>
+      <c r="V34">
+        <v>15820.54941</v>
+      </c>
+      <c r="W34">
+        <v>41657.61918</v>
+      </c>
+      <c r="X34">
+        <v>61902.86963</v>
+      </c>
+      <c r="Y34">
+        <v>18822</v>
+      </c>
+      <c r="Z34">
+        <v>1303</v>
+      </c>
+      <c r="AA34">
+        <v>49089439.53749809</v>
+      </c>
+      <c r="AB34">
+        <v>3211891.634473173</v>
+      </c>
+      <c r="AC34">
+        <v>25292.27293212757</v>
+      </c>
+      <c r="AD34">
+        <v>6227.357904253759</v>
+      </c>
+      <c r="AE34">
+        <v>711.5547687392719</v>
+      </c>
+      <c r="AF34">
+        <v>3377.140846531722</v>
+      </c>
+      <c r="AG34">
+        <v>0.9179305571421851</v>
+      </c>
+      <c r="AH34">
+        <v>2.202542318811933</v>
+      </c>
+      <c r="AI34">
+        <v>0.4963101629097884</v>
+      </c>
+      <c r="AJ34">
+        <v>4.807081114140439</v>
+      </c>
+      <c r="AK34">
+        <v>15.28365372312753</v>
+      </c>
+      <c r="AL34">
+        <v>6.922749973435341</v>
+      </c>
+      <c r="AM34">
+        <v>1.643432179641352</v>
+      </c>
+      <c r="AN34">
+        <v>0.72255689577313</v>
+      </c>
+      <c r="AO34">
+        <v>1.725283506860908</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>North Dakota</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>7415.109</v>
+      </c>
+      <c r="C35">
+        <v>17261.415</v>
+      </c>
+      <c r="D35">
+        <v>2.327870702912122</v>
+      </c>
+      <c r="E35">
+        <v>0.05125020167813588</v>
+      </c>
+      <c r="F35">
+        <v>0.1827653670770825</v>
+      </c>
+      <c r="G35">
+        <v>428934000</v>
+      </c>
+      <c r="H35">
+        <v>37857000</v>
+      </c>
+      <c r="I35">
+        <v>31501000</v>
+      </c>
+      <c r="J35">
+        <v>31190000</v>
+      </c>
+      <c r="K35">
+        <v>1.621</v>
+      </c>
+      <c r="L35">
+        <v>509.715</v>
+      </c>
+      <c r="M35">
+        <v>19.449</v>
+      </c>
+      <c r="N35">
+        <v>2946.227</v>
+      </c>
+      <c r="O35">
+        <v>0.3</v>
+      </c>
+      <c r="P35">
+        <v>61.208</v>
+      </c>
+      <c r="Q35">
+        <v>18.102</v>
+      </c>
+      <c r="R35">
+        <v>205.608</v>
+      </c>
+      <c r="S35">
+        <v>46</v>
+      </c>
+      <c r="T35">
+        <v>9</v>
+      </c>
+      <c r="U35">
+        <v>43</v>
+      </c>
+      <c r="V35">
+        <v>3512.69295</v>
+      </c>
+      <c r="W35">
+        <v>1376.80011</v>
+      </c>
+      <c r="X35">
+        <v>4290.27999</v>
+      </c>
+      <c r="Y35">
+        <v>4281</v>
+      </c>
+      <c r="Z35">
+        <v>449</v>
+      </c>
+      <c r="AA35">
+        <v>809991.676127504</v>
+      </c>
+      <c r="AB35">
+        <v>191620.8071080296</v>
+      </c>
+      <c r="AC35">
+        <v>24849.29537931856</v>
+      </c>
+      <c r="AD35">
+        <v>2193.157397582991</v>
+      </c>
+      <c r="AE35">
+        <v>1824.937295117463</v>
+      </c>
+      <c r="AF35">
+        <v>1806.920232205761</v>
+      </c>
+      <c r="AG35">
+        <v>0.3180208547914031</v>
+      </c>
+      <c r="AH35">
+        <v>0.4901320088877272</v>
+      </c>
+      <c r="AI35">
+        <v>0.6601324337873491</v>
+      </c>
+      <c r="AJ35">
+        <v>8.804132134936383</v>
+      </c>
+      <c r="AK35">
+        <v>4.227054923481544</v>
+      </c>
+      <c r="AL35">
+        <v>10.48820369072647</v>
+      </c>
+      <c r="AM35">
+        <v>1.309536604957174</v>
+      </c>
+      <c r="AN35">
+        <v>0.6536896630550094</v>
+      </c>
+      <c r="AO35">
+        <v>1.002265588731424</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>19274.706</v>
+      </c>
+      <c r="C36">
+        <v>49764.623</v>
+      </c>
+      <c r="D36">
+        <v>2.581861585852464</v>
+      </c>
+      <c r="E36">
+        <v>0.3861671573398637</v>
+      </c>
+      <c r="F36">
+        <v>1.377125942012504</v>
+      </c>
+      <c r="G36">
+        <v>1665471000</v>
+      </c>
+      <c r="H36">
+        <v>751316000</v>
+      </c>
+      <c r="I36">
+        <v>279573000</v>
+      </c>
+      <c r="J36">
+        <v>1300448000</v>
+      </c>
+      <c r="K36">
+        <v>8.102</v>
+      </c>
+      <c r="L36">
+        <v>642.62</v>
+      </c>
+      <c r="M36">
+        <v>5.529</v>
+      </c>
+      <c r="N36">
+        <v>1530.987</v>
+      </c>
+      <c r="O36">
+        <v>38.862</v>
+      </c>
+      <c r="P36">
+        <v>935.956</v>
+      </c>
+      <c r="Q36">
+        <v>312.313</v>
+      </c>
+      <c r="R36">
+        <v>2425.341</v>
+      </c>
+      <c r="S36">
+        <v>132</v>
+      </c>
+      <c r="T36">
+        <v>329</v>
+      </c>
+      <c r="U36">
+        <v>806</v>
+      </c>
+      <c r="V36">
+        <v>15363.22765</v>
+      </c>
+      <c r="W36">
+        <v>43470.1976</v>
+      </c>
+      <c r="X36">
+        <v>51744.08508</v>
+      </c>
+      <c r="Y36">
+        <v>27003</v>
+      </c>
+      <c r="Z36">
+        <v>1223</v>
+      </c>
+      <c r="AA36">
+        <v>41622242.67404459</v>
+      </c>
+      <c r="AB36">
+        <v>3610589.503649727</v>
+      </c>
+      <c r="AC36">
+        <v>33466.96708623714</v>
+      </c>
+      <c r="AD36">
+        <v>15097.39157473372</v>
+      </c>
+      <c r="AE36">
+        <v>5617.906519657548</v>
+      </c>
+      <c r="AF36">
+        <v>26131.97732855326</v>
+      </c>
+      <c r="AG36">
+        <v>1.260776197441723</v>
+      </c>
+      <c r="AH36">
+        <v>4.15211826196958</v>
+      </c>
+      <c r="AI36">
+        <v>0.3611395785855791</v>
+      </c>
+      <c r="AJ36">
+        <v>12.8770758421187</v>
+      </c>
+      <c r="AK36">
+        <v>11.52782464801694</v>
+      </c>
+      <c r="AL36">
+        <v>4.5291263933637</v>
+      </c>
+      <c r="AM36">
+        <v>0.8591944544934215</v>
+      </c>
+      <c r="AN36">
+        <v>0.7568403599803282</v>
+      </c>
+      <c r="AO36">
+        <v>1.557665960764147</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>12664.004</v>
+      </c>
+      <c r="C37">
+        <v>32085.082</v>
+      </c>
+      <c r="D37">
+        <v>2.5335653715839</v>
+      </c>
+      <c r="E37">
+        <v>0.1783153928046685</v>
+      </c>
+      <c r="F37">
+        <v>0.6358975604839961</v>
+      </c>
+      <c r="G37">
+        <v>1550535000</v>
+      </c>
+      <c r="H37">
+        <v>706079000</v>
+      </c>
+      <c r="I37">
+        <v>239679000</v>
+      </c>
+      <c r="J37">
+        <v>497927000</v>
+      </c>
+      <c r="K37">
+        <v>12.912</v>
+      </c>
+      <c r="L37">
+        <v>639.003</v>
+      </c>
+      <c r="M37">
+        <v>47.786</v>
+      </c>
+      <c r="N37">
+        <v>2219.984</v>
+      </c>
+      <c r="O37">
+        <v>14.383</v>
+      </c>
+      <c r="P37">
+        <v>277.411</v>
+      </c>
+      <c r="Q37">
+        <v>75.80599999999998</v>
+      </c>
+      <c r="R37">
+        <v>725.216</v>
+      </c>
+      <c r="S37">
+        <v>131</v>
+      </c>
+      <c r="T37">
+        <v>150</v>
+      </c>
+      <c r="U37">
+        <v>429</v>
+      </c>
+      <c r="V37">
+        <v>11302.12163</v>
+      </c>
+      <c r="W37">
+        <v>14369.57518</v>
+      </c>
+      <c r="X37">
+        <v>18894.0767</v>
+      </c>
+      <c r="Y37">
+        <v>23197</v>
+      </c>
+      <c r="Z37">
+        <v>2207</v>
+      </c>
+      <c r="AA37">
+        <v>10583718.9236346</v>
+      </c>
+      <c r="AB37">
+        <v>1045411.645108428</v>
+      </c>
+      <c r="AC37">
+        <v>48325.72969581316</v>
+      </c>
+      <c r="AD37">
+        <v>22006.45770517276</v>
+      </c>
+      <c r="AE37">
+        <v>7470.107135771073</v>
+      </c>
+      <c r="AF37">
+        <v>15518.95675379605</v>
+      </c>
+      <c r="AG37">
+        <v>2.020647790385961</v>
+      </c>
+      <c r="AH37">
+        <v>5.184725912094329</v>
+      </c>
+      <c r="AI37">
+        <v>2.152538036310172</v>
+      </c>
+      <c r="AJ37">
+        <v>10.45288576093191</v>
+      </c>
+      <c r="AK37">
+        <v>10.12397266967202</v>
+      </c>
+      <c r="AL37">
+        <v>9.514161313963013</v>
+      </c>
+      <c r="AM37">
+        <v>1.159074413535576</v>
+      </c>
+      <c r="AN37">
+        <v>1.043872196088124</v>
+      </c>
+      <c r="AO37">
+        <v>2.27055286591485</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>7590.91</v>
+      </c>
+      <c r="C38">
+        <v>18440.11</v>
+      </c>
+      <c r="D38">
+        <v>2.429235756977754</v>
+      </c>
+      <c r="E38">
+        <v>0.2140502415658041</v>
+      </c>
+      <c r="F38">
+        <v>0.7633330151245431</v>
+      </c>
+      <c r="G38">
+        <v>860112000</v>
+      </c>
+      <c r="H38">
+        <v>488318000</v>
+      </c>
+      <c r="I38">
+        <v>185434000</v>
+      </c>
+      <c r="J38">
+        <v>302411000</v>
+      </c>
+      <c r="K38">
+        <v>3.9</v>
+      </c>
+      <c r="L38">
+        <v>495.18</v>
+      </c>
+      <c r="M38">
+        <v>23.49</v>
+      </c>
+      <c r="N38">
+        <v>2655.313</v>
+      </c>
+      <c r="O38">
+        <v>6.42</v>
+      </c>
+      <c r="P38">
+        <v>234.37</v>
+      </c>
+      <c r="Q38">
+        <v>67.42700000000001</v>
+      </c>
+      <c r="R38">
+        <v>815.431</v>
+      </c>
+      <c r="S38">
+        <v>160</v>
+      </c>
+      <c r="T38">
+        <v>147</v>
+      </c>
+      <c r="U38">
+        <v>294</v>
+      </c>
+      <c r="V38">
+        <v>8674.099330000001</v>
+      </c>
+      <c r="W38">
+        <v>12593.44732</v>
+      </c>
+      <c r="X38">
+        <v>15308.61333</v>
+      </c>
+      <c r="Y38">
+        <v>8255</v>
+      </c>
+      <c r="Z38">
+        <v>396</v>
+      </c>
+      <c r="AA38">
+        <v>54696336.98848939</v>
+      </c>
+      <c r="AB38">
+        <v>1158444.931005402</v>
+      </c>
+      <c r="AC38">
+        <v>46643.53954504609</v>
+      </c>
+      <c r="AD38">
+        <v>26481.29539357412</v>
+      </c>
+      <c r="AE38">
+        <v>10056.01376564456</v>
+      </c>
+      <c r="AF38">
+        <v>16399.63102172384</v>
+      </c>
+      <c r="AG38">
+        <v>0.7875923906458258</v>
+      </c>
+      <c r="AH38">
+        <v>2.739258437513334</v>
+      </c>
+      <c r="AI38">
+        <v>0.8846414716457154</v>
+      </c>
+      <c r="AJ38">
+        <v>8.26887866661925</v>
+      </c>
+      <c r="AK38">
+        <v>47.21531039116294</v>
+      </c>
+      <c r="AL38">
+        <v>4.797092671108419</v>
+      </c>
+      <c r="AM38">
+        <v>1.844571913612153</v>
+      </c>
+      <c r="AN38">
+        <v>1.167273711992627</v>
+      </c>
+      <c r="AO38">
+        <v>1.920487464556007</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>39699.857</v>
+      </c>
+      <c r="C39">
+        <v>88248.64299999998</v>
+      </c>
+      <c r="D39">
+        <v>2.222895739901531</v>
+      </c>
+      <c r="E39">
+        <v>0.3263347516856435</v>
+      </c>
+      <c r="F39">
+        <v>1.163755238592158</v>
+      </c>
+      <c r="G39">
+        <v>3108224000</v>
+      </c>
+      <c r="H39">
+        <v>1745460000</v>
+      </c>
+      <c r="I39">
+        <v>598651000</v>
+      </c>
+      <c r="J39">
+        <v>2619272000</v>
+      </c>
+      <c r="K39">
+        <v>28.37</v>
+      </c>
+      <c r="L39">
+        <v>1066.238</v>
+      </c>
+      <c r="M39">
+        <v>20.929</v>
+      </c>
+      <c r="N39">
+        <v>1626.552</v>
+      </c>
+      <c r="O39">
+        <v>42.738</v>
+      </c>
+      <c r="P39">
+        <v>797.044</v>
+      </c>
+      <c r="Q39">
+        <v>385.567</v>
+      </c>
+      <c r="R39">
+        <v>2870.132</v>
+      </c>
+      <c r="S39">
+        <v>150</v>
+      </c>
+      <c r="T39">
+        <v>376</v>
+      </c>
+      <c r="U39">
+        <v>650</v>
+      </c>
+      <c r="V39">
+        <v>16348.95227</v>
+      </c>
+      <c r="W39">
+        <v>39821.46464999999</v>
+      </c>
+      <c r="X39">
+        <v>43741.89363999999</v>
+      </c>
+      <c r="Y39">
+        <v>23202</v>
+      </c>
+      <c r="Z39">
+        <v>3112</v>
+      </c>
+      <c r="AA39">
+        <v>184644423.8050183</v>
+      </c>
+      <c r="AB39">
+        <v>3905211.441419086</v>
+      </c>
+      <c r="AC39">
+        <v>35221.21014370726</v>
+      </c>
+      <c r="AD39">
+        <v>19778.88770482284</v>
+      </c>
+      <c r="AE39">
+        <v>6783.685047712293</v>
+      </c>
+      <c r="AF39">
+        <v>29680.59236899541</v>
+      </c>
+      <c r="AG39">
+        <v>2.660756791635638</v>
+      </c>
+      <c r="AH39">
+        <v>5.362062822127762</v>
+      </c>
+      <c r="AI39">
+        <v>1.28670955493584</v>
+      </c>
+      <c r="AJ39">
+        <v>13.43377238398791</v>
+      </c>
+      <c r="AK39">
+        <v>47.28154328512408</v>
+      </c>
+      <c r="AL39">
+        <v>13.41263684165158</v>
+      </c>
+      <c r="AM39">
+        <v>0.9174899866534383</v>
+      </c>
+      <c r="AN39">
+        <v>0.9442143911700648</v>
+      </c>
+      <c r="AO39">
+        <v>1.48598962209904</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>1120.334</v>
+      </c>
+      <c r="C40">
+        <v>2782.389</v>
+      </c>
+      <c r="D40">
+        <v>2.4835352671614</v>
+      </c>
+      <c r="E40">
+        <v>0.7086327612709797</v>
+      </c>
+      <c r="F40">
+        <v>2.527083260079924</v>
+      </c>
+      <c r="G40">
+        <v>365183000</v>
+      </c>
+      <c r="H40">
+        <v>119427000</v>
+      </c>
+      <c r="I40">
+        <v>26065000</v>
+      </c>
+      <c r="J40">
+        <v>152093000</v>
+      </c>
+      <c r="K40">
+        <v>0</v>
+      </c>
+      <c r="L40">
+        <v>17.821</v>
+      </c>
+      <c r="M40">
+        <v>5.781</v>
+      </c>
+      <c r="N40">
+        <v>95.789</v>
+      </c>
+      <c r="O40">
+        <v>0.301</v>
+      </c>
+      <c r="P40">
+        <v>52.074</v>
+      </c>
+      <c r="Q40">
+        <v>83.807</v>
+      </c>
+      <c r="R40">
+        <v>331.579</v>
+      </c>
+      <c r="S40">
+        <v>8</v>
+      </c>
+      <c r="T40">
+        <v>27</v>
+      </c>
+      <c r="U40">
+        <v>16</v>
+      </c>
+      <c r="V40">
+        <v>577.9145100000001</v>
+      </c>
+      <c r="W40">
+        <v>4607.05827</v>
+      </c>
+      <c r="X40">
+        <v>2345.64698</v>
+      </c>
+      <c r="Y40">
+        <v>784</v>
+      </c>
+      <c r="Z40">
+        <v>130</v>
+      </c>
+      <c r="AA40">
+        <v>20572011.28945021</v>
+      </c>
+      <c r="AB40">
+        <v>495623.8888186973</v>
+      </c>
+      <c r="AC40">
+        <v>131248.003064992</v>
+      </c>
+      <c r="AD40">
+        <v>42922.4669879014</v>
+      </c>
+      <c r="AE40">
+        <v>9367.848995952758</v>
+      </c>
+      <c r="AF40">
+        <v>54662.73766896002</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40">
+        <v>0.5780235818258632</v>
+      </c>
+      <c r="AI40">
+        <v>6.035139734207476</v>
+      </c>
+      <c r="AJ40">
+        <v>25.2751229722027</v>
+      </c>
+      <c r="AK40">
+        <v>41.50730373082479</v>
+      </c>
+      <c r="AL40">
+        <v>16.58163265306122</v>
+      </c>
+      <c r="AM40">
+        <v>1.38428779024773</v>
+      </c>
+      <c r="AN40">
+        <v>0.5860572716394143</v>
+      </c>
+      <c r="AO40">
+        <v>0.6821145780427709</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>41253.682</v>
+      </c>
+      <c r="C41">
+        <v>90528.641</v>
+      </c>
+      <c r="D41">
+        <v>2.194437844360171</v>
+      </c>
+      <c r="E41">
+        <v>0.3072994434987708</v>
+      </c>
+      <c r="F41">
+        <v>1.095872674733226</v>
+      </c>
+      <c r="G41">
+        <v>1602861000</v>
+      </c>
+      <c r="H41">
+        <v>538146000</v>
+      </c>
+      <c r="I41">
+        <v>140959000</v>
+      </c>
+      <c r="J41">
+        <v>34935000</v>
+      </c>
+      <c r="K41">
+        <v>7.880000000000001</v>
+      </c>
+      <c r="L41">
+        <v>528.727</v>
+      </c>
+      <c r="M41">
+        <v>10.501</v>
+      </c>
+      <c r="N41">
+        <v>1534.821</v>
+      </c>
+      <c r="O41">
+        <v>3.19</v>
+      </c>
+      <c r="P41">
+        <v>287.194</v>
+      </c>
+      <c r="Q41">
+        <v>32.239</v>
+      </c>
+      <c r="R41">
+        <v>1065.195</v>
+      </c>
+      <c r="S41">
+        <v>246</v>
+      </c>
+      <c r="T41">
+        <v>241</v>
+      </c>
+      <c r="U41">
+        <v>607</v>
+      </c>
+      <c r="V41">
+        <v>13786.12467</v>
+      </c>
+      <c r="W41">
+        <v>18090.11602</v>
+      </c>
+      <c r="X41">
+        <v>27112.13889</v>
+      </c>
+      <c r="Y41">
+        <v>9427</v>
+      </c>
+      <c r="Z41">
+        <v>477</v>
+      </c>
+      <c r="AA41">
+        <v>27404341.72626897</v>
+      </c>
+      <c r="AB41">
+        <v>1647195.962801224</v>
+      </c>
+      <c r="AC41">
+        <v>17705.56789867198</v>
+      </c>
+      <c r="AD41">
+        <v>5944.483359691658</v>
+      </c>
+      <c r="AE41">
+        <v>1557.065238613269</v>
+      </c>
+      <c r="AF41">
+        <v>385.8999717006687</v>
+      </c>
+      <c r="AG41">
+        <v>1.490372158032406</v>
+      </c>
+      <c r="AH41">
+        <v>1.11074743901335</v>
+      </c>
+      <c r="AI41">
+        <v>0.6841840188530128</v>
+      </c>
+      <c r="AJ41">
+        <v>3.026581987335652</v>
+      </c>
+      <c r="AK41">
+        <v>16.63696508803064</v>
+      </c>
+      <c r="AL41">
+        <v>5.05993423146282</v>
+      </c>
+      <c r="AM41">
+        <v>1.784402839003196</v>
+      </c>
+      <c r="AN41">
+        <v>1.332219205966154</v>
+      </c>
+      <c r="AO41">
+        <v>2.238849551718271</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>7743.893</v>
+      </c>
+      <c r="C42">
+        <v>17928.202</v>
+      </c>
+      <c r="D42">
+        <v>2.315140717982545</v>
+      </c>
+      <c r="E42">
+        <v>0.05465165999356768</v>
+      </c>
+      <c r="F42">
+        <v>0.1948954418331103</v>
+      </c>
+      <c r="G42">
+        <v>490124000</v>
+      </c>
+      <c r="H42">
+        <v>91923000</v>
+      </c>
+      <c r="I42">
+        <v>125287000</v>
+      </c>
+      <c r="J42">
+        <v>35867000</v>
+      </c>
+      <c r="K42">
+        <v>2.084</v>
+      </c>
+      <c r="L42">
+        <v>591.032</v>
+      </c>
+      <c r="M42">
+        <v>19.046</v>
+      </c>
+      <c r="N42">
+        <v>2590.78</v>
+      </c>
+      <c r="O42">
+        <v>1.01</v>
+      </c>
+      <c r="P42">
+        <v>87.74899999999998</v>
+      </c>
+      <c r="Q42">
+        <v>7.913</v>
+      </c>
+      <c r="R42">
+        <v>132.681</v>
+      </c>
+      <c r="S42">
+        <v>49</v>
+      </c>
+      <c r="T42">
+        <v>12</v>
+      </c>
+      <c r="U42">
+        <v>76</v>
+      </c>
+      <c r="V42">
+        <v>4339.10438</v>
+      </c>
+      <c r="W42">
+        <v>1468.92635</v>
+      </c>
+      <c r="X42">
+        <v>4361.49815</v>
+      </c>
+      <c r="Y42">
+        <v>5897</v>
+      </c>
+      <c r="Z42">
+        <v>996</v>
+      </c>
+      <c r="AA42">
+        <v>1929291.289951148</v>
+      </c>
+      <c r="AB42">
+        <v>200473.9121481326</v>
+      </c>
+      <c r="AC42">
+        <v>27338.1569440148</v>
+      </c>
+      <c r="AD42">
+        <v>5127.284933536558</v>
+      </c>
+      <c r="AE42">
+        <v>6988.263519119207</v>
+      </c>
+      <c r="AF42">
+        <v>2000.591024130585</v>
+      </c>
+      <c r="AG42">
+        <v>0.3526035815319644</v>
+      </c>
+      <c r="AH42">
+        <v>1.151010267923281</v>
+      </c>
+      <c r="AI42">
+        <v>0.7351454002269586</v>
+      </c>
+      <c r="AJ42">
+        <v>5.963928520285497</v>
+      </c>
+      <c r="AK42">
+        <v>9.62365262032484</v>
+      </c>
+      <c r="AL42">
+        <v>16.88994403934204</v>
+      </c>
+      <c r="AM42">
+        <v>1.129265297830886</v>
+      </c>
+      <c r="AN42">
+        <v>0.8169231901926191</v>
+      </c>
+      <c r="AO42">
+        <v>1.742520514424613</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>14064.306</v>
+      </c>
+      <c r="C43">
+        <v>37848.72</v>
+      </c>
+      <c r="D43">
+        <v>2.69111892190059</v>
+      </c>
+      <c r="E43">
+        <v>0.3624985732674711</v>
+      </c>
+      <c r="F43">
+        <v>1.29272047014036</v>
+      </c>
+      <c r="G43">
+        <v>1370242000</v>
+      </c>
+      <c r="H43">
+        <v>431538000</v>
+      </c>
+      <c r="I43">
+        <v>265748000</v>
+      </c>
+      <c r="J43">
+        <v>41857000</v>
+      </c>
+      <c r="K43">
+        <v>5.403</v>
+      </c>
+      <c r="L43">
+        <v>644.527</v>
+      </c>
+      <c r="M43">
+        <v>10.005</v>
+      </c>
+      <c r="N43">
+        <v>1714.396</v>
+      </c>
+      <c r="O43">
+        <v>10.957</v>
+      </c>
+      <c r="P43">
+        <v>556.2380000000001</v>
+      </c>
+      <c r="Q43">
+        <v>85.536</v>
+      </c>
+      <c r="R43">
+        <v>1832.872</v>
+      </c>
+      <c r="S43">
+        <v>179</v>
+      </c>
+      <c r="T43">
+        <v>446</v>
+      </c>
+      <c r="U43">
+        <v>689</v>
+      </c>
+      <c r="V43">
+        <v>14506.4482</v>
+      </c>
+      <c r="W43">
+        <v>32010.94502</v>
+      </c>
+      <c r="X43">
+        <v>36701.24602999999</v>
+      </c>
+      <c r="Y43">
+        <v>20377</v>
+      </c>
+      <c r="Z43">
+        <v>881</v>
+      </c>
+      <c r="AA43">
+        <v>43678261.10548858</v>
+      </c>
+      <c r="AB43">
+        <v>2166842.04930935</v>
+      </c>
+      <c r="AC43">
+        <v>36203.12655223215</v>
+      </c>
+      <c r="AD43">
+        <v>11401.65374152679</v>
+      </c>
+      <c r="AE43">
+        <v>7021.320668175832</v>
+      </c>
+      <c r="AF43">
+        <v>1105.902656681653</v>
+      </c>
+      <c r="AG43">
+        <v>0.8382891639915784</v>
+      </c>
+      <c r="AH43">
+        <v>1.969840248239063</v>
+      </c>
+      <c r="AI43">
+        <v>0.5835874558736722</v>
+      </c>
+      <c r="AJ43">
+        <v>4.666774330122343</v>
+      </c>
+      <c r="AK43">
+        <v>20.15756576230852</v>
+      </c>
+      <c r="AL43">
+        <v>4.323501987534966</v>
+      </c>
+      <c r="AM43">
+        <v>1.233934023905314</v>
+      </c>
+      <c r="AN43">
+        <v>1.393273456067434</v>
+      </c>
+      <c r="AO43">
+        <v>1.877320457830788</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Texas</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>80996.743</v>
+      </c>
+      <c r="C44">
+        <v>200262.234</v>
+      </c>
+      <c r="D44">
+        <v>2.472472677080361</v>
+      </c>
+      <c r="E44">
+        <v>0.2710318311938935</v>
+      </c>
+      <c r="F44">
+        <v>0.9665373109908816</v>
+      </c>
+      <c r="G44">
+        <v>9857146000</v>
+      </c>
+      <c r="H44">
+        <v>2384799000</v>
+      </c>
+      <c r="I44">
+        <v>2241865000</v>
+      </c>
+      <c r="J44">
+        <v>2874177000</v>
+      </c>
+      <c r="K44">
+        <v>21.431</v>
+      </c>
+      <c r="L44">
+        <v>2007.767</v>
+      </c>
+      <c r="M44">
+        <v>36.641</v>
+      </c>
+      <c r="N44">
+        <v>8909.843000000001</v>
+      </c>
+      <c r="O44">
+        <v>61.29800000000001</v>
+      </c>
+      <c r="P44">
+        <v>1459.611</v>
+      </c>
+      <c r="Q44">
+        <v>756.499</v>
+      </c>
+      <c r="R44">
+        <v>5621.731</v>
+      </c>
+      <c r="S44">
+        <v>741</v>
+      </c>
+      <c r="T44">
+        <v>1522</v>
+      </c>
+      <c r="U44">
+        <v>2132</v>
+      </c>
+      <c r="V44">
+        <v>47440.67067</v>
+      </c>
+      <c r="W44">
+        <v>132267.40378</v>
+      </c>
+      <c r="X44">
+        <v>111182.00337</v>
+      </c>
+      <c r="Y44">
+        <v>55701</v>
+      </c>
+      <c r="Z44">
+        <v>774</v>
+      </c>
+      <c r="AA44">
+        <v>453063916.9856837</v>
+      </c>
+      <c r="AB44">
+        <v>9867578.235741533</v>
+      </c>
+      <c r="AC44">
+        <v>49221.19264883463</v>
+      </c>
+      <c r="AD44">
+        <v>11908.38108796889</v>
+      </c>
+      <c r="AE44">
+        <v>11194.64691480472</v>
+      </c>
+      <c r="AF44">
+        <v>14352.0670003112</v>
+      </c>
+      <c r="AG44">
+        <v>1.067404733716611</v>
+      </c>
+      <c r="AH44">
+        <v>4.1996120884263</v>
+      </c>
+      <c r="AI44">
+        <v>0.4112418142497011</v>
+      </c>
+      <c r="AJ44">
+        <v>13.45669154216024</v>
+      </c>
+      <c r="AK44">
+        <v>45.9143982608248</v>
+      </c>
+      <c r="AL44">
+        <v>1.389562126353207</v>
+      </c>
+      <c r="AM44">
+        <v>1.561950936896399</v>
+      </c>
+      <c r="AN44">
+        <v>1.150699232391027</v>
+      </c>
+      <c r="AO44">
+        <v>1.91757652801503</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Utah</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>5905.326</v>
+      </c>
+      <c r="C45">
+        <v>16084.19</v>
+      </c>
+      <c r="D45">
+        <v>2.723675204383297</v>
+      </c>
+      <c r="E45">
+        <v>0.3086304625846872</v>
+      </c>
+      <c r="F45">
+        <v>1.100619274431543</v>
+      </c>
+      <c r="G45">
+        <v>1175592000</v>
+      </c>
+      <c r="H45">
+        <v>271705000</v>
+      </c>
+      <c r="I45">
+        <v>103504000</v>
+      </c>
+      <c r="J45">
+        <v>425960000</v>
+      </c>
+      <c r="K45">
+        <v>2.778</v>
+      </c>
+      <c r="L45">
+        <v>684.64</v>
+      </c>
+      <c r="M45">
+        <v>4.312</v>
+      </c>
+      <c r="N45">
+        <v>1191.276</v>
+      </c>
+      <c r="O45">
+        <v>5.722</v>
+      </c>
+      <c r="P45">
+        <v>253.42</v>
+      </c>
+      <c r="Q45">
+        <v>18.359</v>
+      </c>
+      <c r="R45">
+        <v>662.317</v>
+      </c>
+      <c r="S45">
+        <v>56</v>
+      </c>
+      <c r="T45">
+        <v>126</v>
+      </c>
+      <c r="U45">
+        <v>137</v>
+      </c>
+      <c r="V45">
+        <v>6281.628009999999</v>
+      </c>
+      <c r="W45">
+        <v>15176.52403</v>
+      </c>
+      <c r="X45">
+        <v>12877.99904</v>
+      </c>
+      <c r="Y45">
+        <v>3080</v>
+      </c>
+      <c r="Z45">
+        <v>64</v>
+      </c>
+      <c r="AA45">
+        <v>13939143.85258264</v>
+      </c>
+      <c r="AB45">
+        <v>1115167</v>
+      </c>
+      <c r="AC45">
+        <v>73089.91002966267</v>
+      </c>
+      <c r="AD45">
+        <v>16892.67535387234</v>
+      </c>
+      <c r="AE45">
+        <v>6435.139102435372</v>
+      </c>
+      <c r="AF45">
+        <v>26483.14898045845</v>
+      </c>
+      <c r="AG45">
+        <v>0.405760691750409</v>
+      </c>
+      <c r="AH45">
+        <v>2.257911767027069</v>
+      </c>
+      <c r="AI45">
+        <v>0.3619648175569726</v>
+      </c>
+      <c r="AJ45">
+        <v>2.771935493124894</v>
+      </c>
+      <c r="AK45">
+        <v>12.49960216952496</v>
+      </c>
+      <c r="AL45">
+        <v>2.077922077922078</v>
+      </c>
+      <c r="AM45">
+        <v>0.8914886381500329</v>
+      </c>
+      <c r="AN45">
+        <v>0.8302296346049405</v>
+      </c>
+      <c r="AO45">
+        <v>1.063829866538024</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Vermont</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>2628.694</v>
+      </c>
+      <c r="C46">
+        <v>5998.787</v>
+      </c>
+      <c r="D46">
+        <v>2.282040815705442</v>
+      </c>
+      <c r="E46">
+        <v>0.1165502292380109</v>
+      </c>
+      <c r="F46">
+        <v>0.4156343727851254</v>
+      </c>
+      <c r="G46">
+        <v>228791000</v>
+      </c>
+      <c r="H46">
+        <v>121967000</v>
+      </c>
+      <c r="I46">
+        <v>98406000</v>
+      </c>
+      <c r="J46">
+        <v>101003000</v>
+      </c>
+      <c r="K46">
+        <v>4.419</v>
+      </c>
+      <c r="L46">
+        <v>255.484</v>
+      </c>
+      <c r="M46">
+        <v>13.425</v>
+      </c>
+      <c r="N46">
+        <v>328.885</v>
+      </c>
+      <c r="O46">
+        <v>0.3810000000000001</v>
+      </c>
+      <c r="P46">
+        <v>64.30800000000001</v>
+      </c>
+      <c r="Q46">
+        <v>10.85</v>
+      </c>
+      <c r="R46">
+        <v>125.404</v>
+      </c>
+      <c r="S46">
+        <v>15</v>
+      </c>
+      <c r="T46">
+        <v>8</v>
+      </c>
+      <c r="U46">
+        <v>53</v>
+      </c>
+      <c r="V46">
+        <v>1904.42352</v>
+      </c>
+      <c r="W46">
+        <v>1181.43887</v>
+      </c>
+      <c r="X46">
+        <v>4041.90031</v>
+      </c>
+      <c r="Y46">
+        <v>2846</v>
+      </c>
+      <c r="Z46">
+        <v>71</v>
+      </c>
+      <c r="AA46">
+        <v>834419.6243916424</v>
+      </c>
+      <c r="AB46">
+        <v>91172.09090909091</v>
+      </c>
+      <c r="AC46">
+        <v>38139.54387778729</v>
+      </c>
+      <c r="AD46">
+        <v>20331.9437746331</v>
+      </c>
+      <c r="AE46">
+        <v>16404.31640596674</v>
+      </c>
+      <c r="AF46">
+        <v>16837.23726146636</v>
+      </c>
+      <c r="AG46">
+        <v>1.729658217344335</v>
+      </c>
+      <c r="AH46">
+        <v>0.592461280089569</v>
+      </c>
+      <c r="AI46">
+        <v>4.081973942259453</v>
+      </c>
+      <c r="AJ46">
+        <v>8.652036617651749</v>
+      </c>
+      <c r="AK46">
+        <v>9.1521387309594</v>
+      </c>
+      <c r="AL46">
+        <v>2.494729444834856</v>
+      </c>
+      <c r="AM46">
+        <v>0.7876399258080997</v>
+      </c>
+      <c r="AN46">
+        <v>0.6771404093044611</v>
+      </c>
+      <c r="AO46">
+        <v>1.311264403747751</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>59467.334</v>
+      </c>
+      <c r="C47">
+        <v>129519.217</v>
+      </c>
+      <c r="D47">
+        <v>2.177989297451942</v>
+      </c>
+      <c r="E47">
+        <v>0.2485080109772436</v>
+      </c>
+      <c r="F47">
+        <v>0.8862142266891387</v>
+      </c>
+      <c r="G47">
+        <v>2069884000</v>
+      </c>
+      <c r="H47">
+        <v>1920178000</v>
+      </c>
+      <c r="I47">
+        <v>490532000</v>
+      </c>
+      <c r="J47">
+        <v>927405000</v>
+      </c>
+      <c r="K47">
+        <v>2.583</v>
+      </c>
+      <c r="L47">
+        <v>591.072</v>
+      </c>
+      <c r="M47">
+        <v>5.19</v>
+      </c>
+      <c r="N47">
+        <v>1642.968</v>
+      </c>
+      <c r="O47">
+        <v>18.586</v>
+      </c>
+      <c r="P47">
+        <v>527.798</v>
+      </c>
+      <c r="Q47">
+        <v>85.864</v>
+      </c>
+      <c r="R47">
+        <v>1349.257</v>
+      </c>
+      <c r="S47">
+        <v>249</v>
+      </c>
+      <c r="T47">
+        <v>329</v>
+      </c>
+      <c r="U47">
+        <v>424</v>
+      </c>
+      <c r="V47">
+        <v>16435.50682</v>
+      </c>
+      <c r="W47">
+        <v>33987.16298</v>
+      </c>
+      <c r="X47">
+        <v>31660.56325</v>
+      </c>
+      <c r="Y47">
+        <v>14042</v>
+      </c>
+      <c r="Z47">
+        <v>501</v>
+      </c>
+      <c r="AA47">
+        <v>106178733.2850093</v>
+      </c>
+      <c r="AB47">
+        <v>2710154.225044428</v>
+      </c>
+      <c r="AC47">
+        <v>15981.2887071422</v>
+      </c>
+      <c r="AD47">
+        <v>14825.42934150073</v>
+      </c>
+      <c r="AE47">
+        <v>3787.329875534995</v>
+      </c>
+      <c r="AF47">
+        <v>7160.366017345518</v>
+      </c>
+      <c r="AG47">
+        <v>0.4370025986681825</v>
+      </c>
+      <c r="AH47">
+        <v>3.521422968635728</v>
+      </c>
+      <c r="AI47">
+        <v>0.3158917276538557</v>
+      </c>
+      <c r="AJ47">
+        <v>6.363798742567206</v>
+      </c>
+      <c r="AK47">
+        <v>39.17811477436074</v>
+      </c>
+      <c r="AL47">
+        <v>3.56786782509614</v>
+      </c>
+      <c r="AM47">
+        <v>1.515012604886619</v>
+      </c>
+      <c r="AN47">
+        <v>0.9680125410691163</v>
+      </c>
+      <c r="AO47">
+        <v>1.339205486181614</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>7052.32</v>
+      </c>
+      <c r="C48">
+        <v>18470.58</v>
+      </c>
+      <c r="D48">
+        <v>2.619078544365542</v>
+      </c>
+      <c r="E48">
+        <v>0.3236779787099268</v>
+      </c>
+      <c r="F48">
+        <v>1.154280815619214</v>
+      </c>
+      <c r="G48">
+        <v>1748297000</v>
+      </c>
+      <c r="H48">
+        <v>657970000</v>
+      </c>
+      <c r="I48">
+        <v>346714000</v>
+      </c>
+      <c r="J48">
+        <v>1496629000</v>
+      </c>
+      <c r="K48">
+        <v>17.33</v>
+      </c>
+      <c r="L48">
+        <v>428.99</v>
+      </c>
+      <c r="M48">
+        <v>10.83</v>
+      </c>
+      <c r="N48">
+        <v>1312.886</v>
+      </c>
+      <c r="O48">
+        <v>12</v>
+      </c>
+      <c r="P48">
+        <v>334.47</v>
+      </c>
+      <c r="Q48">
+        <v>260.651</v>
+      </c>
+      <c r="R48">
+        <v>1431.464</v>
+      </c>
+      <c r="S48">
+        <v>97</v>
+      </c>
+      <c r="T48">
+        <v>274</v>
+      </c>
+      <c r="U48">
+        <v>356</v>
+      </c>
+      <c r="V48">
+        <v>9281.516370000001</v>
+      </c>
+      <c r="W48">
+        <v>26819.52774</v>
+      </c>
+      <c r="X48">
+        <v>22381.71117</v>
+      </c>
+      <c r="Y48">
+        <v>8388</v>
+      </c>
+      <c r="Z48">
+        <v>423</v>
+      </c>
+      <c r="AA48">
+        <v>64941721.52451983</v>
+      </c>
+      <c r="AB48">
+        <v>2339297.023427264</v>
+      </c>
+      <c r="AC48">
+        <v>94653.0644949969</v>
+      </c>
+      <c r="AD48">
+        <v>35622.59550052028</v>
+      </c>
+      <c r="AE48">
+        <v>18771.14849669041</v>
+      </c>
+      <c r="AF48">
+        <v>81027.72084038508</v>
+      </c>
+      <c r="AG48">
+        <v>4.039721205622508</v>
+      </c>
+      <c r="AH48">
+        <v>3.587765718898556</v>
+      </c>
+      <c r="AI48">
+        <v>0.8249002579051038</v>
+      </c>
+      <c r="AJ48">
+        <v>18.20870102217031</v>
+      </c>
+      <c r="AK48">
+        <v>27.76121239592518</v>
+      </c>
+      <c r="AL48">
+        <v>5.042918454935622</v>
+      </c>
+      <c r="AM48">
+        <v>1.045087851307641</v>
+      </c>
+      <c r="AN48">
+        <v>1.021643642111351</v>
+      </c>
+      <c r="AO48">
+        <v>1.590584371748909</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>West Virginia</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>34374.676</v>
+      </c>
+      <c r="C49">
+        <v>71077.96000000001</v>
+      </c>
+      <c r="D49">
+        <v>2.067741962135149</v>
+      </c>
+      <c r="E49">
+        <v>0.1274754086920896</v>
+      </c>
+      <c r="F49">
+        <v>0.4545950864589515</v>
+      </c>
+      <c r="G49">
+        <v>1188666000</v>
+      </c>
+      <c r="H49">
+        <v>458536000</v>
+      </c>
+      <c r="I49">
+        <v>134558000</v>
+      </c>
+      <c r="J49">
+        <v>160403000</v>
+      </c>
+      <c r="K49">
+        <v>6.027</v>
+      </c>
+      <c r="L49">
+        <v>318.952</v>
+      </c>
+      <c r="M49">
+        <v>25.699</v>
+      </c>
+      <c r="N49">
+        <v>1004.108</v>
+      </c>
+      <c r="O49">
+        <v>9.533000000000001</v>
+      </c>
+      <c r="P49">
+        <v>235.438</v>
+      </c>
+      <c r="Q49">
+        <v>19.5</v>
+      </c>
+      <c r="R49">
+        <v>397.208</v>
+      </c>
+      <c r="S49">
+        <v>53</v>
+      </c>
+      <c r="T49">
+        <v>33</v>
+      </c>
+      <c r="U49">
+        <v>177</v>
+      </c>
+      <c r="V49">
+        <v>3521.68149</v>
+      </c>
+      <c r="W49">
+        <v>4290.7423</v>
+      </c>
+      <c r="X49">
+        <v>7499.983749999999</v>
+      </c>
+      <c r="Y49">
+        <v>7317</v>
+      </c>
+      <c r="Z49">
+        <v>1461</v>
+      </c>
+      <c r="AA49">
+        <v>3028619.187663389</v>
+      </c>
+      <c r="AB49">
+        <v>329187.644451483</v>
+      </c>
+      <c r="AC49">
+        <v>16723.41187057141</v>
+      </c>
+      <c r="AD49">
+        <v>6451.169954793299</v>
+      </c>
+      <c r="AE49">
+        <v>1893.104416615221</v>
+      </c>
+      <c r="AF49">
+        <v>2256.719241801537</v>
+      </c>
+      <c r="AG49">
+        <v>1.889626025232637</v>
+      </c>
+      <c r="AH49">
+        <v>4.049049006532506</v>
+      </c>
+      <c r="AI49">
+        <v>2.559386042138894</v>
+      </c>
+      <c r="AJ49">
+        <v>4.909266681436426</v>
+      </c>
+      <c r="AK49">
+        <v>9.200282084432118</v>
+      </c>
+      <c r="AL49">
+        <v>19.96719967199672</v>
+      </c>
+      <c r="AM49">
+        <v>1.504962903388517</v>
+      </c>
+      <c r="AN49">
+        <v>0.7690976920240584</v>
+      </c>
+      <c r="AO49">
+        <v>2.360005113344412</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>11745.76</v>
+      </c>
+      <c r="C50">
+        <v>29934.38</v>
+      </c>
+      <c r="D50">
+        <v>2.548526446990233</v>
+      </c>
+      <c r="E50">
+        <v>0.2596719891977051</v>
+      </c>
+      <c r="F50">
+        <v>0.9260265300692767</v>
+      </c>
+      <c r="G50">
+        <v>1266752000</v>
+      </c>
+      <c r="H50">
+        <v>293057000</v>
+      </c>
+      <c r="I50">
+        <v>178280000</v>
+      </c>
+      <c r="J50">
+        <v>828372000</v>
+      </c>
+      <c r="K50">
+        <v>8.24</v>
+      </c>
+      <c r="L50">
+        <v>511.79</v>
+      </c>
+      <c r="M50">
+        <v>44.94</v>
+      </c>
+      <c r="N50">
+        <v>2880.605</v>
+      </c>
+      <c r="O50">
+        <v>15.35</v>
+      </c>
+      <c r="P50">
+        <v>366.78</v>
+      </c>
+      <c r="Q50">
+        <v>352.676</v>
+      </c>
+      <c r="R50">
+        <v>1910.718</v>
+      </c>
+      <c r="S50">
+        <v>104</v>
+      </c>
+      <c r="T50">
+        <v>155</v>
+      </c>
+      <c r="U50">
+        <v>336</v>
+      </c>
+      <c r="V50">
+        <v>14032.68569</v>
+      </c>
+      <c r="W50">
+        <v>20854.05388</v>
+      </c>
+      <c r="X50">
+        <v>31279.94133</v>
+      </c>
+      <c r="Y50">
+        <v>14336</v>
+      </c>
+      <c r="Z50">
+        <v>922</v>
+      </c>
+      <c r="AA50">
+        <v>27064932.81285626</v>
+      </c>
+      <c r="AB50">
+        <v>1618888.264154293</v>
+      </c>
+      <c r="AC50">
+        <v>42317.6294281024</v>
+      </c>
+      <c r="AD50">
+        <v>9789.980617604238</v>
+      </c>
+      <c r="AE50">
+        <v>5955.693754138219</v>
+      </c>
+      <c r="AF50">
+        <v>27672.92992204949</v>
+      </c>
+      <c r="AG50">
+        <v>1.610035366068114</v>
+      </c>
+      <c r="AH50">
+        <v>4.185070069251323</v>
+      </c>
+      <c r="AI50">
+        <v>1.560088939649831</v>
+      </c>
+      <c r="AJ50">
+        <v>18.45777346526279</v>
+      </c>
+      <c r="AK50">
+        <v>16.71822164143921</v>
+      </c>
+      <c r="AL50">
+        <v>6.431361607142858</v>
+      </c>
+      <c r="AM50">
+        <v>0.741126839847291</v>
+      </c>
+      <c r="AN50">
+        <v>0.7432607630723164</v>
+      </c>
+      <c r="AO50">
+        <v>1.074170812711048</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>6732.288</v>
+      </c>
+      <c r="C51">
+        <v>15787.322</v>
+      </c>
+      <c r="D51">
+        <v>2.345015840082896</v>
+      </c>
+      <c r="E51">
+        <v>0.09255413932774666</v>
+      </c>
+      <c r="F51">
+        <v>0.3300609694177175</v>
+      </c>
+      <c r="G51">
+        <v>443316000</v>
+      </c>
+      <c r="H51">
+        <v>104013000</v>
+      </c>
+      <c r="I51">
+        <v>25971000</v>
+      </c>
+      <c r="J51">
+        <v>43379000</v>
+      </c>
+      <c r="K51">
+        <v>8.338999999999999</v>
+      </c>
+      <c r="L51">
+        <v>807.0549999999998</v>
+      </c>
+      <c r="M51">
+        <v>5.067</v>
+      </c>
+      <c r="N51">
+        <v>1914.119</v>
+      </c>
+      <c r="O51">
+        <v>6.735</v>
+      </c>
+      <c r="P51">
+        <v>105.648</v>
+      </c>
+      <c r="Q51">
+        <v>12.775</v>
+      </c>
+      <c r="R51">
+        <v>195.657</v>
+      </c>
+      <c r="S51">
+        <v>66</v>
+      </c>
+      <c r="T51">
+        <v>11</v>
+      </c>
+      <c r="U51">
+        <v>54</v>
+      </c>
+      <c r="V51">
+        <v>4286.4512</v>
+      </c>
+      <c r="W51">
+        <v>1356.85342</v>
+      </c>
+      <c r="X51">
+        <v>3681.08069</v>
+      </c>
+      <c r="Y51">
+        <v>3121</v>
+      </c>
+      <c r="Z51">
+        <v>205</v>
+      </c>
+      <c r="AA51">
+        <v>599940.4314770896</v>
+      </c>
+      <c r="AB51">
+        <v>77474.81818181818</v>
+      </c>
+      <c r="AC51">
+        <v>28080.50662423937</v>
+      </c>
+      <c r="AD51">
+        <v>6588.387821569738</v>
+      </c>
+      <c r="AE51">
+        <v>1645.054177016216</v>
+      </c>
+      <c r="AF51">
+        <v>2747.711106418175</v>
+      </c>
+      <c r="AG51">
+        <v>1.033262912688726</v>
+      </c>
+      <c r="AH51">
+        <v>6.374943207632895</v>
+      </c>
+      <c r="AI51">
+        <v>0.2647170839430568</v>
+      </c>
+      <c r="AJ51">
+        <v>6.529283388787521</v>
+      </c>
+      <c r="AK51">
+        <v>7.743682987020987</v>
+      </c>
+      <c r="AL51">
+        <v>6.568407561678949</v>
+      </c>
+      <c r="AM51">
+        <v>1.539735247656616</v>
+      </c>
+      <c r="AN51">
+        <v>0.8106992131839857</v>
+      </c>
+      <c r="AO51">
+        <v>1.466960508273998</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>782300.1160000002</v>
+      </c>
+      <c r="C52">
+        <v>1893421.538999999</v>
+      </c>
+      <c r="D52">
+        <v>2.420326292013485</v>
+      </c>
+      <c r="E52">
+        <v>15.28058625518086</v>
+      </c>
+      <c r="F52">
+        <v>54.49270177745638</v>
+      </c>
+      <c r="G52">
+        <v>82694707000</v>
+      </c>
+      <c r="H52">
+        <v>28058662000</v>
+      </c>
+      <c r="I52">
+        <v>11944044000</v>
+      </c>
+      <c r="J52">
+        <v>38683151000</v>
+      </c>
+      <c r="K52">
+        <v>594.4660000000001</v>
+      </c>
+      <c r="L52">
+        <v>29310.517</v>
+      </c>
+      <c r="M52">
+        <v>906.298</v>
+      </c>
+      <c r="N52">
+        <v>90314.76999999999</v>
+      </c>
+      <c r="O52">
+        <v>869.106</v>
+      </c>
+      <c r="P52">
+        <v>19088.81</v>
+      </c>
+      <c r="Q52">
+        <v>8091.313999999996</v>
+      </c>
+      <c r="R52">
+        <v>62483.25299999999</v>
+      </c>
+      <c r="S52">
+        <v>6466</v>
+      </c>
+      <c r="T52">
+        <v>13545</v>
+      </c>
+      <c r="U52">
+        <v>22098</v>
+      </c>
+      <c r="V52">
+        <v>515468.6584799999</v>
+      </c>
+      <c r="W52">
+        <v>1263163.13189</v>
+      </c>
+      <c r="X52">
+        <v>1414138.875</v>
+      </c>
+      <c r="Y52">
+        <v>618005</v>
+      </c>
+      <c r="Z52">
+        <v>42635</v>
+      </c>
+      <c r="AA52">
+        <v>4145885299.821218</v>
+      </c>
+      <c r="AB52">
+        <v>100317767.4272307</v>
+      </c>
+      <c r="AC52">
+        <v>43674.74716891346</v>
+      </c>
+      <c r="AD52">
+        <v>14819.02546372164</v>
+      </c>
+      <c r="AE52">
+        <v>6308.180061323367</v>
+      </c>
+      <c r="AF52">
+        <v>20430.28992922004</v>
+      </c>
+      <c r="AG52">
+        <v>2.028166203960169</v>
+      </c>
+      <c r="AH52">
+        <v>4.552960608859326</v>
+      </c>
+      <c r="AI52">
+        <v>1.003488133779226</v>
+      </c>
+      <c r="AJ52">
+        <v>12.94957226378722</v>
+      </c>
+      <c r="AK52">
+        <v>41.3275275770924</v>
+      </c>
+      <c r="AL52">
+        <v>6.898811498288849</v>
+      </c>
+      <c r="AM52">
+        <v>1.254392462786538</v>
+      </c>
+      <c r="AN52">
+        <v>1.07230805412547</v>
+      </c>
+      <c r="AO52">
+        <v>1.562647091502947</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>